--- a/docs/xlsx/jobs-2026-09-01.xlsx
+++ b/docs/xlsx/jobs-2026-09-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="484">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1441 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Agronomy &amp; Conservation Specialist</t>
+  </si>
+  <si>
+    <t>Pheasants Forever and Quail Forever</t>
+  </si>
+  <si>
+    <t>Austin, MN</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$49,500 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-agronomy--conservation-specialist-austin-minnesota/5926666868</t>
+  </si>
+  <si>
+    <t>Conservation Coordinator</t>
+  </si>
+  <si>
+    <t>Jefferson County SWCD</t>
+  </si>
+  <si>
+    <t>Redmond, OR</t>
+  </si>
+  <si>
+    <t>$27 - $32 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-hydrology-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-coordinator-redmond-oregon/8835960413</t>
+  </si>
+  <si>
+    <t>Conservation Specialist</t>
+  </si>
+  <si>
+    <t>Manistee Conservation District</t>
+  </si>
+  <si>
+    <t>Bear Lake, MI</t>
+  </si>
+  <si>
+    <t>$45,000 - $54,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-specialist-bear-lake-michigan/1563699417</t>
+  </si>
+  <si>
+    <t>Director and Professor</t>
+  </si>
+  <si>
+    <t>Univ. of Georgia, Skidaway Institute of Oceanography</t>
+  </si>
+  <si>
+    <t>Savannah, GA</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Compensation determined by experience, expected hire at the Professor level</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-and-professor-savannah-georgia/6234217577</t>
+  </si>
+  <si>
+    <t>Director of Operations &amp; Programs</t>
+  </si>
+  <si>
+    <t>Jubilee College</t>
+  </si>
+  <si>
+    <t>Dunsmuir, CA</t>
+  </si>
+  <si>
+    <t>$80,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-operations--programs-dunsmuir-california/1109969544</t>
+  </si>
+  <si>
+    <t>Drinking Water Protection Specialist (Natural Resource Specialist 3)</t>
+  </si>
+  <si>
+    <t>Oregon Department of Environmental Quality</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$5,453 - $8,345 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-drinking-water-protection-specialist-natural-resource-specialist-3-portland-oregon/2215597616</t>
+  </si>
+  <si>
+    <t>Ecological Restoration Technician</t>
+  </si>
+  <si>
+    <t>EcoNorth LLC</t>
+  </si>
+  <si>
+    <t>Ashland, WI</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19 - $23 per hour</t>
+  </si>
+  <si>
+    <t>botany-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecological-restoration-technician-ashland-wisconsin/5847899921</t>
+  </si>
+  <si>
+    <t>Environmental Analyst – Underground Storage Tanks and Technical Assistance Specialist</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Lowell, MA</t>
+  </si>
+  <si>
+    <t>$55,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-analyst--underground-storage-tanks-and-technical-assistance-specialist-lowell-massachusetts/2952776330</t>
+  </si>
+  <si>
+    <t>Field Technician</t>
+  </si>
+  <si>
+    <t>Friends of Hopewell Valley Open Space</t>
+  </si>
+  <si>
+    <t>Titusville, NJ</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>botany-land-trust-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-technician-titusville-new-jersey/4502974957</t>
+  </si>
+  <si>
+    <t>Fisheries Technician</t>
+  </si>
+  <si>
+    <t>FISHBIO</t>
+  </si>
+  <si>
+    <t>Oakdale and Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$20 - $26.75 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-oakdale-and-sacramento-california/3671209571</t>
+  </si>
+  <si>
+    <t>Habitat Specialist Intership</t>
+  </si>
+  <si>
+    <t>North Platte, NE</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$22 per hour</t>
+  </si>
+  <si>
+    <t>restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-specialist-intership-north-platte-nebraska/9148611264</t>
+  </si>
+  <si>
+    <t>Land Disposal and Waste Containment Section Leader</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>$11,437 - $14,315 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-disposal-and-waste-containment-section-leader-oakland-california/6802960919</t>
+  </si>
+  <si>
+    <t>Marine Reserves Ecologist</t>
+  </si>
+  <si>
+    <t>Oregon Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Newport, OR</t>
+  </si>
+  <si>
+    <t>$4,519 - $6,276 per month</t>
+  </si>
+  <si>
+    <t>ecology-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-reserves-ecologist-newport-oregon/6616043563</t>
+  </si>
+  <si>
+    <t>Natural Resources Technician II</t>
+  </si>
+  <si>
+    <t>MetroParks of Butler County</t>
+  </si>
+  <si>
+    <t>Hamilton, OH</t>
+  </si>
+  <si>
+    <t>$15 - $19.25 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-technician-ii-hamilton-ohio/1760950460</t>
+  </si>
+  <si>
+    <t>Oceans Special Project Attorney</t>
+  </si>
+  <si>
+    <t>Center for Biological Diversity</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>Dependant on MOU</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-oceans-special-project-attorney-remote-remote/1282054074</t>
+  </si>
+  <si>
+    <t>Parks Planner</t>
+  </si>
+  <si>
+    <t>Kitsap County Parks</t>
+  </si>
+  <si>
+    <t>Silverdale, WA</t>
+  </si>
+  <si>
+    <t>$80,875.23 - $103,465.54 per year</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-parks-planner-silverdale-washington/3173965281</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Northwest Conservation District</t>
+  </si>
+  <si>
+    <t>Torrington, CT</t>
+  </si>
+  <si>
+    <t>$21.22 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-assistant-torrington-connecticut/6479381679</t>
+  </si>
+  <si>
+    <t>Rangeland Ecologist</t>
+  </si>
+  <si>
+    <t>University of Nevada Reno</t>
+  </si>
+  <si>
+    <t>Reno, NV</t>
+  </si>
+  <si>
+    <t>Salary commensurate with experience.</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rangeland-ecologist-reno-nevada/4351274941</t>
+  </si>
+  <si>
+    <t>Research Data Specialist III</t>
+  </si>
+  <si>
+    <t>Glendale, CA</t>
+  </si>
+  <si>
+    <t>$8,392 - $10,820 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-data-specialist-iii-glendale-california/6017409508</t>
+  </si>
+  <si>
+    <t>Senior Environmental Scientist (Specialist)</t>
+  </si>
+  <si>
+    <t>Palm Desert, CA</t>
+  </si>
+  <si>
+    <t>$7,820 - $10,732 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-environmental-scientist-specialist-palm-desert-california/4422661924</t>
+  </si>
+  <si>
+    <t>STEM &amp; Environmental Educator</t>
+  </si>
+  <si>
+    <t>Mill River Park Collaborative</t>
+  </si>
+  <si>
+    <t>Stamford, CT</t>
+  </si>
+  <si>
+    <t>$21 - $23 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stem--environmental-educator-stamford-connecticut/2408581963</t>
+  </si>
+  <si>
+    <t>Stormwater Compliance Specialist (Natural Resource Specialist 3) - Three Openings</t>
+  </si>
+  <si>
+    <t>Bend, Eugene, Medford, or Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stormwater-compliance-specialist-natural-resource-specialist-3---three-openings-bend-eugene-medford-or-portland-oregon/9765302669</t>
+  </si>
+  <si>
+    <t>TCEQ - Transitions Hiring Program (Texas Statewide)</t>
+  </si>
+  <si>
+    <t>Texas Commission on Environmental Quality</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$4,454 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tceq---transitions-hiring-program-texas-statewide-austin-texas/3978303534</t>
+  </si>
+  <si>
+    <t>Temporary Conservation Grazing Associate</t>
+  </si>
+  <si>
+    <t>Santa Lucia Conservancy</t>
+  </si>
+  <si>
+    <t>CARMEL, CA</t>
+  </si>
+  <si>
+    <t>$24 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-temporary-conservation-grazing-associate-carmel-california/2735838971</t>
+  </si>
+  <si>
+    <t>Temporary Ecological Restoration Laborer</t>
+  </si>
+  <si>
+    <t>Sound Native Plants</t>
+  </si>
+  <si>
+    <t>Portland, OR, OR</t>
+  </si>
+  <si>
+    <t>$20 - $30.24 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration-botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-temporary-ecological-restoration-laborer-portland-or-oregon/9406369526</t>
+  </si>
+  <si>
+    <t>Trail Crew Member</t>
+  </si>
+  <si>
+    <t>Outdoor Recreation Designs</t>
+  </si>
+  <si>
+    <t>Severance, CO</t>
+  </si>
+  <si>
+    <t>$23 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-trail-crew-member-severance-colorado/7244270361</t>
+  </si>
+  <si>
+    <t>Vice President of Finance and Operations</t>
+  </si>
+  <si>
+    <t>Forest Society of Maine</t>
+  </si>
+  <si>
+    <t>Bangor, ME</t>
+  </si>
+  <si>
+    <t>$100,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-of-finance-and-operations-bangor-maine/5789734546</t>
+  </si>
+  <si>
+    <t>Watercraft Inspector - Natural Resource Technician 2 - Career Seasonal - 2026-07173</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Clarkston, WA</t>
+  </si>
+  <si>
+    <t>$3,327 - $4,406 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watercraft-inspector---natural-resource-technician-2---career-seasonal---2026-07173-clarkston-washington/5224760036</t>
+  </si>
+  <si>
+    <t>Waterfowl Survey &amp; Sea Duck Specialist - Fish and Wildlife Biologist 4 - Permanent - 2026-07259</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$5,928 - $7,973 per month</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-waterfowl-survey--sea-duck-specialist---fish-and-wildlife-biologist-4---permanent---2026-07259-olympia-washington/2655828090</t>
+  </si>
+  <si>
+    <t>Conservation Grazing Program Manager</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/conservation-grazing-program-manager-3/</t>
+  </si>
+  <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>FITCHBURG ART MUSEUM</t>
+  </si>
+  <si>
+    <t>FITCHBURG, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Economic Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce3c10c172834e9986c5c1dec39b88d8-accounting-manager-fitchburg-art-museum-fitchburg</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f0b2175b34aa49ff8692f5057456b139-administrative-coordinator-careers-in-nonprofits-inc-washington</t>
+  </si>
+  <si>
+    <t>Asociación Conciencia busca Asistente de Programa Porvenir - Salta</t>
+  </si>
+  <si>
+    <t>Asociación Conciencia</t>
+  </si>
+  <si>
+    <t>Salta, Salta, AR</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f35dce954d7c4f63bb1e2993cfd95c8e-asociacion-conciencia-busca-asistente-de-programa-porvenir-salta-asociacion-conciencia-salta</t>
+  </si>
+  <si>
+    <t>Associate II, Education Agency Practice</t>
+  </si>
+  <si>
+    <t>Project Evident</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee676e14d2a742b8baaca6d294e98cbc-associate-ii-education-agency-practice-project-evident-boston</t>
+  </si>
+  <si>
+    <t>Auxiliar de Cozinha e Limpeza (CLT)</t>
+  </si>
+  <si>
+    <t>Eco Caminhos</t>
+  </si>
+  <si>
+    <t>Nova Friburgo, Rio de Janeiro, BR</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40170d78699a45e5ac6fac31a8ac83d5-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Bilingual Farmworker Advocacy Network Manager</t>
+  </si>
+  <si>
+    <t>Farmworker Advocacy Network</t>
+  </si>
+  <si>
+    <t>Remote (North Carolina)</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0cda03142a1f40508042899f1a90c326-bilingual-farmworker-advocacy-network-manager-farmworker-advocacy-network-raleigh</t>
+  </si>
+  <si>
+    <t>Bookkeeper</t>
+  </si>
+  <si>
+    <t>Unitarian Universalist Church at Washington Crossing</t>
+  </si>
+  <si>
+    <t>Hopewell Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 18000.00 - 21000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2675a54c24a408fbb44459cd88bded0-bookkeeper-unitarian-universalist-church-at-washington-crossing-hopewell-township</t>
+  </si>
+  <si>
+    <t>Career Pathways / Internship Coordinator</t>
+  </si>
+  <si>
+    <t>New Haven Academy</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1cf7478dc1048b8b97b668ca42b3073-career-pathways-internship-coordinator-new-haven-academy-new-haven</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>New Visions for Public Schools</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 266000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/fbcfe146ee79461a91207b4ad892cf57-chief-financial-officer-new-visions-for-public-schools-new-york</t>
+  </si>
+  <si>
+    <t>Community &amp; Children’s Engagement Manager</t>
+  </si>
+  <si>
+    <t>Everybody's Place of Galveston County</t>
+  </si>
+  <si>
+    <t>Dickinson, Texas</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d849e6360874ea7960e70fe7ff711f5-community-childrens-engagement-manager-everybodys-place-of-galveston-county-dickinson</t>
+  </si>
+  <si>
+    <t>Community Programs &amp; Partnerships Manager</t>
+  </si>
+  <si>
+    <t>City Park Conservancy</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c5f274fa8a347a8a15db93e4586185d-community-programs-partnerships-manager-city-park-conservancy-new-orleans</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>John F. Kennedy Library Foundation</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 117000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f45eb1e44ec34b11a617d8c16b7801d8-controller-john-f-kennedy-library-foundation-boston</t>
+  </si>
+  <si>
+    <t>Deputy Legal Director - ACLU of Montana</t>
+  </si>
+  <si>
+    <t>ACLU of Montana</t>
+  </si>
+  <si>
+    <t>Remote (Montana)</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07f5c27ce93a4ad387a4ab37e67bbfc9-deputy-legal-director-aclu-of-montana-aclu-of-montana-missoula</t>
+  </si>
+  <si>
+    <t>Director of Early Age Education - Sipe's Orchard Home</t>
+  </si>
+  <si>
+    <t>Armstrong McGuire &amp; Associates</t>
+  </si>
+  <si>
+    <t>Conover, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/61d16d8798f64cf4b41ca1b47eaf0e0d-director-of-early-age-education-sipes-orchard-home-armstrong-mcguire-associates-conover</t>
+  </si>
+  <si>
+    <t>Director of Health Care Policy, Medicaid</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 130610.00 - 145122.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7ea2ad2b9ab41a7b3f6ddd9010447e4-director-of-health-care-policy-medicaid-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Director, Education Agency Practice</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Research Social Science, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/237e3fde16a74bd58d7a7be3619b66e9-director-education-agency-practice-project-evident-boston</t>
+  </si>
+  <si>
+    <t>Director, Evidence for Outcomes</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/512eccd9a4a24399a802193a6e7f44ce-director-evidence-for-outcomes-project-evident-boston</t>
+  </si>
+  <si>
+    <t>Domestic Violence Advocate</t>
+  </si>
+  <si>
+    <t>Barrier Free Living</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5192ba488a974994bc8bb8499441abda-domestic-violence-advocate-barrier-free-living-new-york</t>
+  </si>
+  <si>
+    <t>Donor Relations Manager</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/281d370bf90b43019c2283b905aff76b-donor-relations-manager-center-for-biological-diversity-oakland</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the CEO</t>
+  </si>
+  <si>
+    <t>Success Academy Charter Schools</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf66f3f4c6924a57a1c6a2aba099b6ab-executive-assistant-to-the-ceo-success-academy-charter-schools-new-york</t>
+  </si>
+  <si>
+    <t>Executive Assistant/Donor Manager</t>
+  </si>
+  <si>
+    <t>Ray of Hope Institute</t>
+  </si>
+  <si>
+    <t>Haverstraw, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/948b4273cf1d40d3b06a78d713a0d7d5-executive-assistantdonor-manager-ray-of-hope-institute-haverstraw</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Kentucky Waterways Alliance</t>
+  </si>
+  <si>
+    <t>Louisville, KY</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d48afe31c03b47038204c7af2f37e142-executive-director-kentucky-waterways-alliance-louisville</t>
+  </si>
+  <si>
+    <t>Hudson River Park Friends</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 265000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Community Development, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/cbec54e255844695878940cecbfbade8-executive-director-hudson-river-park-friends-new-york</t>
+  </si>
+  <si>
+    <t>American Parkinson Disease Association</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c636be9dbe7848fb99336514c5683629-executive-director-american-parkinson-disease-association-minneapolis</t>
+  </si>
+  <si>
+    <t>Executive Director- Environmental Justice Focus</t>
+  </si>
+  <si>
+    <t>Michigan Environmental Justice Coalition</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d47ba638a69c4ca9b049e10e432f457b-executive-director-environmental-justice-focus-michigan-environmental-justice-coalition-detroit</t>
+  </si>
+  <si>
+    <t>Exhibit and Sponsorship Coordinator</t>
+  </si>
+  <si>
+    <t>International Sign Association</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b61cf103fc74734b4d307cd0147fcd3-exhibit-and-sponsorship-coordinator-international-sign-association-alexandria</t>
+  </si>
+  <si>
+    <t>Finance Coordinator [Part-time]</t>
+  </si>
+  <si>
+    <t>NYC FIRST</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/360710216ffd44b6a85db0438f331272-finance-coordinator-part-time-nyc-first-new-york</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Women's Global Education Project</t>
+  </si>
+  <si>
+    <t>Oak Park, IL</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8cffa8cdaf4464a9471d77274275aa6-finance-manager-womens-global-education-project-oak-park</t>
+  </si>
+  <si>
+    <t>Freelancer season Fundraiser</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Poverty, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4196b32fee544f49952915b0a79ae0b1-freelancer-season-fundraiser-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Housing Counselor</t>
+  </si>
+  <si>
+    <t>Allston Brighton Community Development Corporation</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d84f85a36164455ba3451d0d6c29b75b-housing-counselor-allston-brighton-community-development-corporation-boston</t>
+  </si>
+  <si>
+    <t>Lead, Direct Care Workforce Development</t>
+  </si>
+  <si>
+    <t>National Council on Aging</t>
+  </si>
+  <si>
+    <t>Arlington, VA</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Disability, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f11a3555c8ce4f23a6f597a9ffa349f4-lead-direct-care-workforce-development-national-council-on-aging-arlington</t>
+  </si>
+  <si>
+    <t>Local Food Access Delivery Driver</t>
+  </si>
+  <si>
+    <t>The People's Market</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 80.00 - 125.00/day</t>
+  </si>
+  <si>
+    <t>Agriculture, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/99b70cdc50274c6484c9fdad8449e5b3-local-food-access-delivery-driver-the-peoples-market-hyattsville</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>University of Texas at Tyler</t>
+  </si>
+  <si>
+    <t>Tyler, Texas</t>
+  </si>
+  <si>
+    <t>USD 130000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47e4fdbb4a2047a5a8acbb85f010436d-major-gifts-officer-university-of-texas-at-tyler-tyler</t>
+  </si>
+  <si>
+    <t>Manager, Arts in Public Health</t>
+  </si>
+  <si>
+    <t>Sing for Hope</t>
+  </si>
+  <si>
+    <t>USD 77500.00 - 77500.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/353f0801455347b2a2c866bdb80dce36-manager-arts-in-public-health-sing-for-hope-new-york</t>
+  </si>
+  <si>
+    <t>MANAGING ATTORNEY OF THE ENERGY UNIT</t>
+  </si>
+  <si>
+    <t>Community Legal Services, Inc.</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e283d90227ba4ced8ad5fcf8a7d993a9-managing-attorney-of-the-energy-unit-community-legal-services-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Managing Attorney, Metropolitan Equity</t>
+  </si>
+  <si>
+    <t>Public Advocates Inc.</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 171600.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Transportation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce2bd37cd12f46c5ada66520f8e41321-managing-attorney-metropolitan-equity-public-advocates-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Managing Director - Boston City Singers</t>
+  </si>
+  <si>
+    <t>Boston City Singers</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f0407033ffc44c88bbf2611ec9db02c-managing-director-boston-city-singers-boston-city-singers-boston</t>
+  </si>
+  <si>
+    <t>Medical Referral Coordinator II</t>
+  </si>
+  <si>
+    <t>Bread for the City</t>
+  </si>
+  <si>
+    <t>USD 24.04 - 26.44/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/941e5be4396e4d4b9e02a7889156ecbe-medical-referral-coordinator-ii-bread-for-the-city-washington</t>
+  </si>
+  <si>
+    <t>National Executive Assistant</t>
+  </si>
+  <si>
+    <t>After-School All-Stars</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Sports Recreation, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf0554a846894ec4acd09662ade469d1-national-executive-assistant-after-school-all-stars-los-angeles</t>
+  </si>
+  <si>
+    <t>Nonpartisan Election Protection Hotline Captain</t>
+  </si>
+  <si>
+    <t>Promote the Vote</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12afe66365e545d9b38db871d0448ea6-nonpartisan-election-protection-hotline-captain-promote-the-vote-detroit</t>
+  </si>
+  <si>
+    <t>Paralegal (full-time) at Law Firm Exclusively Serving Nonprofit/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1c9a2e8a937d452884436889946e1cb9-paralegal-full-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Part-Time Development Director</t>
+  </si>
+  <si>
+    <t>Family Reading Partners</t>
+  </si>
+  <si>
+    <t>Carrboro, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6cec7efe38714988a2087782d678e3cc-part-time-development-director-family-reading-partners-carrboro</t>
+  </si>
+  <si>
+    <t>Pianist</t>
+  </si>
+  <si>
+    <t>National Dance Institute</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8678cdc81764e709816b71e0e746a7c-pianist-national-dance-institute-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate, BioQuest</t>
+  </si>
+  <si>
+    <t>RTW Foundation</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d8fc7f6df5840f58fbe6c6420f7c369-program-associate-bioquest-rtw-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>Culver City, California</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efe386f51879474e82c12c7785b2dbb2-program-coordinator-baby2baby-culver-city</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Partnership with Children</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/240c35b8715c45fcbda6b8e6becb194e-program-director-partnership-with-children-kings-county</t>
+  </si>
+  <si>
+    <t>Program Support Specialist</t>
+  </si>
+  <si>
+    <t>The Ark</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b0912efc029423e8fbb9193e178e8de-program-support-specialist-the-ark-chicago</t>
+  </si>
+  <si>
+    <t>Recruitment Manager</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5468d644faff45cd968bfe387519ca0f-recruitment-manager-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Regional Campaign Manager</t>
+  </si>
+  <si>
+    <t>Riders Alliance</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Transportation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2764bcc6abc64fbf88b3c7d040f90630-regional-campaign-manager-riders-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Second Grade Lead Teacher (Immediate Opening)</t>
+  </si>
+  <si>
+    <t>Harlem Academy</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b0ec9dcbb194cccbbc3b0d88e3afa1d-second-grade-lead-teacher-immediate-opening-harlem-academy-new-york</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Denton, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 16.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db3c4abd6bb14d4e9d7d27c6d95a72ee-service-enriched-housing-super-hero-community-housing-resource-partners-inc-denton</t>
+  </si>
+  <si>
+    <t>Special Assistant Attorney General: Civil Enforcement (3906)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 91356.00 - 190493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/63e9749137674330ba61bb6b8b48594b-special-assistant-attorney-general-civil-enforcement-3906-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Congregation Rodeph Sholom &amp; Rodeph Sholom School</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/551bce29c7584e1b98726e689eee3168-staff-accountant-congregation-rodeph-sholom-rodeph-sholom-school-new-york</t>
+  </si>
+  <si>
+    <t>Telehealth Coordinator</t>
+  </si>
+  <si>
+    <t>Remote Area Medical</t>
+  </si>
+  <si>
+    <t>Rockford, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/384c1aa2c3ef4bca80893d8ccef4f273-telehealth-coordinator-remote-area-medical-rockford</t>
+  </si>
+  <si>
+    <t>The Moth - Senior Manager, Global Community</t>
+  </si>
+  <si>
+    <t>The Moth</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61410e1e08c34d02b7f41b6ab7238d12-the-moth-senior-manager-global-community-the-moth-new-york</t>
+  </si>
+  <si>
+    <t>The Moth - Vice President, Business &amp; Partnerships</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5ef4e03e6a54469af1d7b4d48200350-the-moth-vice-president-business-partnerships-the-moth-new-york</t>
+  </si>
+  <si>
+    <t>TRABAJADOR/A SOCIAL</t>
+  </si>
+  <si>
+    <t>Médicos Sin Fronteras en México AC</t>
+  </si>
+  <si>
+    <t>Tapachula, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>MXN 21500.00 - 21500.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca3b559f8c0a4a69a2c249365d7894fd-trabajadora-social-medicos-sin-fronteras-en-mexico-ac-tapachula</t>
+  </si>
+  <si>
+    <t>Vice President of Advancement</t>
+  </si>
+  <si>
+    <t>United Through Reading</t>
+  </si>
+  <si>
+    <t>USD 93500.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f808df352f14e2a8c24b913e50e1d42-vice-president-of-advancement-united-through-reading-san-diego</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1482,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1508,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +1890,706 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" t="s">
+        <v>98</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" t="s">
+        <v>161</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +2597,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +2636,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2671,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +2710,1402 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" t="s">
+        <v>232</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" t="s">
+        <v>237</v>
+      </c>
+      <c r="F11" t="s">
+        <v>238</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" t="s">
+        <v>243</v>
+      </c>
+      <c r="F12" t="s">
+        <v>244</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>254</v>
+      </c>
+      <c r="F14" t="s">
+        <v>255</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" t="s">
+        <v>260</v>
+      </c>
+      <c r="F15" t="s">
+        <v>261</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" t="s">
+        <v>267</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F17" t="s">
+        <v>271</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" t="s">
+        <v>270</v>
+      </c>
+      <c r="F18" t="s">
+        <v>274</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>276</v>
+      </c>
+      <c r="B19" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F19" t="s">
+        <v>279</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" t="s">
+        <v>282</v>
+      </c>
+      <c r="F20" t="s">
+        <v>283</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" t="s">
+        <v>288</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>290</v>
+      </c>
+      <c r="B22" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" t="s">
+        <v>292</v>
+      </c>
+      <c r="D22" t="s">
+        <v>183</v>
+      </c>
+      <c r="E22" t="s">
+        <v>293</v>
+      </c>
+      <c r="F22" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" t="s">
+        <v>298</v>
+      </c>
+      <c r="F23" t="s">
+        <v>299</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B24" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" t="s">
+        <v>302</v>
+      </c>
+      <c r="D24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" t="s">
+        <v>303</v>
+      </c>
+      <c r="F24" t="s">
+        <v>304</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" t="s">
+        <v>306</v>
+      </c>
+      <c r="C25" t="s">
+        <v>307</v>
+      </c>
+      <c r="D25" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" t="s">
+        <v>308</v>
+      </c>
+      <c r="F25" t="s">
+        <v>309</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" t="s">
+        <v>313</v>
+      </c>
+      <c r="D26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" t="s">
+        <v>314</v>
+      </c>
+      <c r="F26" t="s">
+        <v>299</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D27" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" t="s">
+        <v>318</v>
+      </c>
+      <c r="F27" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" t="s">
+        <v>322</v>
+      </c>
+      <c r="F28" t="s">
+        <v>323</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>325</v>
+      </c>
+      <c r="B29" t="s">
+        <v>326</v>
+      </c>
+      <c r="C29" t="s">
+        <v>327</v>
+      </c>
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" t="s">
+        <v>328</v>
+      </c>
+      <c r="F29" t="s">
+        <v>329</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>331</v>
+      </c>
+      <c r="B30" t="s">
+        <v>332</v>
+      </c>
+      <c r="C30" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" t="s">
+        <v>333</v>
+      </c>
+      <c r="E30" t="s">
+        <v>334</v>
+      </c>
+      <c r="F30" t="s">
+        <v>335</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" t="s">
+        <v>338</v>
+      </c>
+      <c r="C31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" t="s">
+        <v>339</v>
+      </c>
+      <c r="F31" t="s">
+        <v>340</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B32" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" t="s">
+        <v>344</v>
+      </c>
+      <c r="D32" t="s">
+        <v>345</v>
+      </c>
+      <c r="E32" t="s">
+        <v>346</v>
+      </c>
+      <c r="F32" t="s">
+        <v>347</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>349</v>
+      </c>
+      <c r="B33" t="s">
+        <v>350</v>
+      </c>
+      <c r="C33" t="s">
+        <v>351</v>
+      </c>
+      <c r="D33" t="s">
+        <v>333</v>
+      </c>
+      <c r="E33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F33" t="s">
+        <v>353</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>355</v>
+      </c>
+      <c r="B34" t="s">
+        <v>356</v>
+      </c>
+      <c r="C34" t="s">
+        <v>357</v>
+      </c>
+      <c r="D34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" t="s">
+        <v>358</v>
+      </c>
+      <c r="F34" t="s">
+        <v>359</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>361</v>
+      </c>
+      <c r="B35" t="s">
+        <v>362</v>
+      </c>
+      <c r="C35" t="s">
+        <v>230</v>
+      </c>
+      <c r="D35" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" t="s">
+        <v>363</v>
+      </c>
+      <c r="F35" t="s">
+        <v>364</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>366</v>
+      </c>
+      <c r="B36" t="s">
+        <v>367</v>
+      </c>
+      <c r="C36" t="s">
+        <v>368</v>
+      </c>
+      <c r="D36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="s">
+        <v>369</v>
+      </c>
+      <c r="F36" t="s">
+        <v>370</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>372</v>
+      </c>
+      <c r="B37" t="s">
+        <v>373</v>
+      </c>
+      <c r="C37" t="s">
+        <v>374</v>
+      </c>
+      <c r="D37" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" t="s">
+        <v>375</v>
+      </c>
+      <c r="F37" t="s">
+        <v>376</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" t="s">
+        <v>379</v>
+      </c>
+      <c r="C38" t="s">
+        <v>380</v>
+      </c>
+      <c r="D38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" t="s">
+        <v>381</v>
+      </c>
+      <c r="F38" t="s">
+        <v>382</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>384</v>
+      </c>
+      <c r="B39" t="s">
+        <v>385</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" t="s">
+        <v>386</v>
+      </c>
+      <c r="F39" t="s">
+        <v>387</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>389</v>
+      </c>
+      <c r="B40" t="s">
+        <v>390</v>
+      </c>
+      <c r="C40" t="s">
+        <v>391</v>
+      </c>
+      <c r="D40" t="s">
+        <v>183</v>
+      </c>
+      <c r="E40" t="s">
+        <v>392</v>
+      </c>
+      <c r="F40" t="s">
+        <v>393</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>395</v>
+      </c>
+      <c r="B41" t="s">
+        <v>396</v>
+      </c>
+      <c r="C41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" t="s">
+        <v>333</v>
+      </c>
+      <c r="E41" t="s">
+        <v>397</v>
+      </c>
+      <c r="F41" t="s">
+        <v>398</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>400</v>
+      </c>
+      <c r="B42" t="s">
+        <v>401</v>
+      </c>
+      <c r="C42" t="s">
+        <v>368</v>
+      </c>
+      <c r="D42" t="s">
+        <v>183</v>
+      </c>
+      <c r="E42" t="s">
+        <v>293</v>
+      </c>
+      <c r="F42" t="s">
+        <v>370</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>403</v>
+      </c>
+      <c r="B43" t="s">
+        <v>404</v>
+      </c>
+      <c r="C43" t="s">
+        <v>405</v>
+      </c>
+      <c r="D43" t="s">
+        <v>213</v>
+      </c>
+      <c r="E43" t="s">
+        <v>406</v>
+      </c>
+      <c r="F43" t="s">
+        <v>407</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>409</v>
+      </c>
+      <c r="B44" t="s">
+        <v>410</v>
+      </c>
+      <c r="C44" t="s">
+        <v>230</v>
+      </c>
+      <c r="D44" t="s">
+        <v>213</v>
+      </c>
+      <c r="E44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F44" t="s">
+        <v>412</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>414</v>
+      </c>
+      <c r="B45" t="s">
+        <v>415</v>
+      </c>
+      <c r="C45" t="s">
+        <v>230</v>
+      </c>
+      <c r="D45" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" t="s">
+        <v>416</v>
+      </c>
+      <c r="F45" t="s">
+        <v>203</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>418</v>
+      </c>
+      <c r="B46" t="s">
+        <v>419</v>
+      </c>
+      <c r="C46" t="s">
+        <v>420</v>
+      </c>
+      <c r="D46" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" t="s">
+        <v>421</v>
+      </c>
+      <c r="F46" t="s">
+        <v>422</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>424</v>
+      </c>
+      <c r="B47" t="s">
+        <v>425</v>
+      </c>
+      <c r="C47" t="s">
+        <v>426</v>
+      </c>
+      <c r="D47" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" t="s">
+        <v>427</v>
+      </c>
+      <c r="F47" t="s">
+        <v>428</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>430</v>
+      </c>
+      <c r="B48" t="s">
+        <v>431</v>
+      </c>
+      <c r="C48" t="s">
+        <v>432</v>
+      </c>
+      <c r="D48" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" t="s">
+        <v>433</v>
+      </c>
+      <c r="F48" t="s">
+        <v>177</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>435</v>
+      </c>
+      <c r="B49" t="s">
+        <v>436</v>
+      </c>
+      <c r="C49" t="s">
+        <v>201</v>
+      </c>
+      <c r="D49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" t="s">
+        <v>437</v>
+      </c>
+      <c r="F49" t="s">
+        <v>309</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>439</v>
+      </c>
+      <c r="B50" t="s">
+        <v>440</v>
+      </c>
+      <c r="C50" t="s">
+        <v>230</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" t="s">
+        <v>441</v>
+      </c>
+      <c r="F50" t="s">
+        <v>442</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>444</v>
+      </c>
+      <c r="B51" t="s">
+        <v>445</v>
+      </c>
+      <c r="C51" t="s">
+        <v>230</v>
+      </c>
+      <c r="D51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" t="s">
+        <v>446</v>
+      </c>
+      <c r="F51" t="s">
+        <v>428</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>448</v>
+      </c>
+      <c r="B52" t="s">
+        <v>449</v>
+      </c>
+      <c r="C52" t="s">
+        <v>450</v>
+      </c>
+      <c r="D52" t="s">
+        <v>213</v>
+      </c>
+      <c r="E52" t="s">
+        <v>451</v>
+      </c>
+      <c r="F52" t="s">
+        <v>177</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" t="s">
+        <v>454</v>
+      </c>
+      <c r="C53" t="s">
+        <v>230</v>
+      </c>
+      <c r="D53" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" t="s">
+        <v>455</v>
+      </c>
+      <c r="F53" t="s">
+        <v>177</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>457</v>
+      </c>
+      <c r="B54" t="s">
+        <v>458</v>
+      </c>
+      <c r="C54" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" t="s">
+        <v>183</v>
+      </c>
+      <c r="E54" t="s">
+        <v>459</v>
+      </c>
+      <c r="F54" t="s">
+        <v>460</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>462</v>
+      </c>
+      <c r="B55" t="s">
+        <v>463</v>
+      </c>
+      <c r="C55" t="s">
+        <v>464</v>
+      </c>
+      <c r="D55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" t="s">
+        <v>177</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>466</v>
+      </c>
+      <c r="B56" t="s">
+        <v>467</v>
+      </c>
+      <c r="C56" t="s">
+        <v>230</v>
+      </c>
+      <c r="D56" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" t="s">
+        <v>468</v>
+      </c>
+      <c r="F56" t="s">
+        <v>469</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>471</v>
+      </c>
+      <c r="B57" t="s">
+        <v>467</v>
+      </c>
+      <c r="C57" t="s">
+        <v>230</v>
+      </c>
+      <c r="D57" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" t="s">
+        <v>472</v>
+      </c>
+      <c r="F57" t="s">
+        <v>469</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>474</v>
+      </c>
+      <c r="B58" t="s">
+        <v>475</v>
+      </c>
+      <c r="C58" t="s">
+        <v>476</v>
+      </c>
+      <c r="D58" t="s">
+        <v>183</v>
+      </c>
+      <c r="E58" t="s">
+        <v>477</v>
+      </c>
+      <c r="F58" t="s">
+        <v>177</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>479</v>
+      </c>
+      <c r="B59" t="s">
+        <v>480</v>
+      </c>
+      <c r="C59" t="s">
+        <v>201</v>
+      </c>
+      <c r="D59" t="s">
+        <v>183</v>
+      </c>
+      <c r="E59" t="s">
+        <v>481</v>
+      </c>
+      <c r="F59" t="s">
+        <v>482</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-01.xlsx
+++ b/docs/xlsx/jobs-2026-09-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="877">
   <si>
     <t>Title</t>
   </si>
@@ -211,6 +211,24 @@
     <t>https://www.conservationjobboard.com/job-listing-field-technician-titusville-new-jersey/4502974957</t>
   </si>
   <si>
+    <t>Finance Director</t>
+  </si>
+  <si>
+    <t>Mad Agriculture</t>
+  </si>
+  <si>
+    <t>Boulder, CO</t>
+  </si>
+  <si>
+    <t>$135,000 - $155,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-finance-director-boulder-colorado/6111779215</t>
+  </si>
+  <si>
     <t>Fisheries Technician</t>
   </si>
   <si>
@@ -412,6 +430,24 @@
     <t>https://www.conservationjobboard.com/job-listing-stem--environmental-educator-stamford-connecticut/2408581963</t>
   </si>
   <si>
+    <t>Stewardship Coordinator</t>
+  </si>
+  <si>
+    <t>Kalkaska Conservation District</t>
+  </si>
+  <si>
+    <t>Kalkaska, MI</t>
+  </si>
+  <si>
+    <t>$40,000 - $44,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stewardship-coordinator-kalkaska-michigan/3421702363</t>
+  </si>
+  <si>
     <t>Stormwater Compliance Specialist (Natural Resource Specialist 3) - Three Openings</t>
   </si>
   <si>
@@ -553,9 +589,66 @@
     <t>Environmental</t>
   </si>
   <si>
+    <t>NAFSN</t>
+  </si>
+  <si>
     <t>https://greenjobs.greenjobsearch.org/jobs/conservation-grazing-program-manager-3/</t>
   </si>
   <si>
+    <t>Director of Development (Part-Time)</t>
+  </si>
+  <si>
+    <t>Eat for the Earth</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part-Time</t>
+  </si>
+  <si>
+    <t>Sustainable Agriculture / Food</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/director-of-development-13/</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>West Virginia Land Trust</t>
+  </si>
+  <si>
+    <t>Charleston, West Virginia, United States</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/executive-director-211/</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>The Museum of Modern Art</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 87002.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb297d2fe0044f40941f9ad0e2a3b841-accountant-the-museum-of-modern-art-new-york</t>
+  </si>
+  <si>
     <t>Accounting Manager</t>
   </si>
   <si>
@@ -565,9 +658,6 @@
     <t>FITCHBURG, Massachusetts</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -577,6 +667,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ce3c10c172834e9986c5c1dec39b88d8-accounting-manager-fitchburg-art-museum-fitchburg</t>
   </si>
   <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Betty and Leonard Phillips Deaf Action Center</t>
+  </si>
+  <si>
+    <t>Shreveport, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 18.00/hour</t>
+  </si>
+  <si>
+    <t>Communications Access, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4148ed0af8394fa58ec0ba961ab7f20c-administrative-assistant-betty-and-leonard-phillips-deaf-action-center-shreveport</t>
+  </si>
+  <si>
     <t>Administrative Coordinator</t>
   </si>
   <si>
@@ -595,6 +703,27 @@
     <t>https://www.idealist.org/en/job/f0b2175b34aa49ff8692f5057456b139-administrative-coordinator-careers-in-nonprofits-inc-washington</t>
   </si>
   <si>
+    <t>Advisor, Support Services</t>
+  </si>
+  <si>
+    <t>THE ERIC AND WENDY SCHMIDT FUND FOR STRATEGIC INNOVATION</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 52.88 - 62.50/hour</t>
+  </si>
+  <si>
+    <t>Environment, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dec733f059a14cb3af5b0029b4e4e180-advisor-support-services-the-eric-and-wendy-schmidt-fund-for-strategic-innovation-new-york</t>
+  </si>
+  <si>
     <t>Asociación Conciencia busca Asistente de Programa Porvenir - Salta</t>
   </si>
   <si>
@@ -613,15 +742,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/f35dce954d7c4f63bb1e2993cfd95c8e-asociacion-conciencia-busca-asistente-de-programa-porvenir-salta-asociacion-conciencia-salta</t>
   </si>
   <si>
+    <t>Assistant Director</t>
+  </si>
+  <si>
+    <t>Catholic Charities Archdiocese of NY</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6dcb16822174c80a919b4b6aad164f0-assistant-director-catholic-charities-archdiocese-of-ny-new-york</t>
+  </si>
+  <si>
+    <t>Associate Director of Children &amp; Family Services (AD of CFS)</t>
+  </si>
+  <si>
+    <t>Safe &amp; Sound</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 113854.00 - 113854.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a85c7ec6ebc6439e9d55be91613ab9d3-associate-director-of-children-family-services-ad-of-cfs-safe-sound-san-francisco</t>
+  </si>
+  <si>
+    <t>Associate Director, Development &amp; Corporate Sponsorships</t>
+  </si>
+  <si>
+    <t>University of California Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8800bef525dd4f2198ff3b048d32569d-associate-director-development-corporate-sponsorships-university-of-california-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Associate II, Education Agency Practice</t>
   </si>
   <si>
     <t>Project Evident</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 78000.00/year</t>
   </si>
   <si>
@@ -646,6 +817,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/40170d78699a45e5ac6fac31a8ac83d5-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
   </si>
   <si>
+    <t>Base Building Canvasser (Lexington KY)</t>
+  </si>
+  <si>
+    <t>VOCAL-KY</t>
+  </si>
+  <si>
+    <t>Louisville, Kentucky</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ce528b19bdb4b4abc6d86d7418fc978-base-building-canvasser-lexington-ky-vocal-ky-louisville</t>
+  </si>
+  <si>
+    <t>Behavioral Health Coordinator</t>
+  </si>
+  <si>
+    <t>Barrier Free Living</t>
+  </si>
+  <si>
+    <t>USD 30.92 - 30.92/hour</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2672f003dc0347a98769bf5c9e2789e1-behavioral-health-coordinator-barrier-free-living-new-york</t>
+  </si>
+  <si>
     <t>Bilingual Farmworker Advocacy Network Manager</t>
   </si>
   <si>
@@ -655,9 +862,6 @@
     <t>Remote (North Carolina)</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 40000.00 - 46000.00/year</t>
   </si>
   <si>
@@ -667,6 +871,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/0cda03142a1f40508042899f1a90c326-bilingual-farmworker-advocacy-network-manager-farmworker-advocacy-network-raleigh</t>
   </si>
   <si>
+    <t>Bilingual Web Content &amp; Parent Support Coordinator</t>
+  </si>
+  <si>
+    <t>National School Choice Awareness Foundation</t>
+  </si>
+  <si>
+    <t>Remote (South Carolina)</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6977d01e1e64d80b09de3f353efd3f5-bilingual-web-content-parent-support-coordinator-national-school-choice-awareness-foundation-miami</t>
+  </si>
+  <si>
+    <t>Remote (Virginia)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97c45dd5c5ad490b8d545f0fc4a03a29-bilingual-web-content-parent-support-coordinator-national-school-choice-awareness-foundation-miami</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bc9bf1e5e114f8fa757ac4a8b3e17c6-bilingual-web-content-parent-support-coordinator-national-school-choice-awareness-foundation-miami</t>
+  </si>
+  <si>
     <t>Bookkeeper</t>
   </si>
   <si>
@@ -700,15 +934,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/e1cf7478dc1048b8b97b668ca42b3073-career-pathways-internship-coordinator-new-haven-academy-new-haven</t>
   </si>
   <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Northwest Arkansas Equality, Inc.</t>
+  </si>
+  <si>
+    <t>Fayetteville, Arkansas</t>
+  </si>
+  <si>
+    <t>Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03eee838648b466aa06f81d670229af1-chief-executive-officer-northwest-arkansas-equality-inc-fayetteville</t>
+  </si>
+  <si>
     <t>Chief Financial Officer</t>
   </si>
   <si>
     <t>New Visions for Public Schools</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 200000.00 - 266000.00/year</t>
   </si>
   <si>
@@ -718,6 +964,54 @@
     <t>https://www.idealist.org/en/job/fbcfe146ee79461a91207b4ad892cf57-chief-financial-officer-new-visions-for-public-schools-new-york</t>
   </si>
   <si>
+    <t>College Access Program Advisor</t>
+  </si>
+  <si>
+    <t>College Visions</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/597c8b747ced4953a6ef1bb63a1e7c01-college-access-program-advisor-college-visions-providence</t>
+  </si>
+  <si>
+    <t>College and Career Advisor</t>
+  </si>
+  <si>
+    <t>Comprehensive Youth Development</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/398095b52ce84a40a6564d3700884d25-college-and-career-advisor-comprehensive-youth-development-new-york</t>
+  </si>
+  <si>
+    <t>Communications and Community Coordinator</t>
+  </si>
+  <si>
+    <t>St. Matthew's Lutheran Church Renton, WA</t>
+  </si>
+  <si>
+    <t>Renton, Washington</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Hunger Food Security, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e60ec889d5c34a4b8021e681be1638c1-communications-and-community-coordinator-st-matthews-lutheran-church-renton-wa-renton</t>
+  </si>
+  <si>
     <t>Community &amp; Children’s Engagement Manager</t>
   </si>
   <si>
@@ -754,6 +1048,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/3c5f274fa8a347a8a15db93e4586185d-community-programs-partnerships-manager-city-park-conservancy-new-orleans</t>
   </si>
   <si>
+    <t>Community Supports Coordinator</t>
+  </si>
+  <si>
+    <t>Access Living of Metropolitan Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49148346093b42579829de82c0eca4b2-community-supports-coordinator-access-living-of-metropolitan-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Community Training Manager</t>
+  </si>
+  <si>
+    <t>Safety Saints</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a14f68c4a5949bf85e7133494c2c789-community-training-manager-safety-saints-new-york</t>
+  </si>
+  <si>
     <t>Controller</t>
   </si>
   <si>
@@ -787,6 +1114,132 @@
     <t>https://www.idealist.org/en/nonprofit-job/07f5c27ce93a4ad387a4ab37e67bbfc9-deputy-legal-director-aclu-of-montana-aclu-of-montana-missoula</t>
   </si>
   <si>
+    <t>Development Coordinator- UCLA Latino Policy And Politics Institute</t>
+  </si>
+  <si>
+    <t>UCLA Latino Policy and Politics Institute</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bbc7fab142c44ef81f0709ceb29fd62-development-coordinator-ucla-latino-policy-and-politics-institute-ucla-latino-policy-and-politics-institute-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Vineyard Conservation Society</t>
+  </si>
+  <si>
+    <t>Tisbury, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e46c6432fcf04af8954313d19dffc80f-development-director-vineyard-conservation-society-tisbury</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Oakland Theater Project</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Urban Areas, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d5e7883c9e644f1bcfec4ab1412c07f-development-manager-oakland-theater-project-oakland</t>
+  </si>
+  <si>
+    <t>Development Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Mercado Global</t>
+  </si>
+  <si>
+    <t>Remote (MX)</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b14f3ae3098f44ca8506fd4a9f5ff7ea-development-operations-coordinator-mercado-global-brooklyn</t>
+  </si>
+  <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>Smithsonian Institution, Office of Advancement</t>
+  </si>
+  <si>
+    <t>USD 151661.00 - 228300.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a00769a88ad498aaab99440d2e9a7e2-director-of-advancement-smithsonian-institution-office-of-advancement-washington</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>MAKE-A-WISH NORTHEASTERN &amp; CENTRAL CALIFORNIA</t>
+  </si>
+  <si>
+    <t>Sacramento County, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93ef7d1b00c541d5a21ffb240437661a-director-of-development-make-a-wish-northeastern-central-california-sacramento-county</t>
+  </si>
+  <si>
+    <t>Academy of American Poets</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98c4786bcc58477ab7739b81fb73f226-director-of-development-academy-of-american-poets-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>Court Appointed Special Advocates (CASA-NYC)</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f94caf61ed264f64a85b03d6b1f6f16d-director-of-development-and-communications-court-appointed-special-advocates-casa-nyc-new-york</t>
+  </si>
+  <si>
     <t>Director of Early Age Education - Sipe's Orchard Home</t>
   </si>
   <si>
@@ -844,18 +1297,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/512eccd9a4a24399a802193a6e7f44ce-director-evidence-for-outcomes-project-evident-boston</t>
   </si>
   <si>
+    <t>Director, Individual Giving</t>
+  </si>
+  <si>
+    <t>Trust for the National Mall</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc871288294a492cb7e6d00aa8b670f8-director-individual-giving-trust-for-the-national-mall-washington</t>
+  </si>
+  <si>
+    <t>Docente de regularización y nivelación Educativa (presencial en Mazapil, Zacatecas)</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Concepción del Oro, Zacatecas, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 15000.00 - 15000.00/month</t>
+  </si>
+  <si>
+    <t>Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/faef85648cfa46d48f19b98f5d1e8939-docente-de-regularizacion-y-nivelacion-educativa-presencial-en-mazapil-zacatecas-educacion-para-compartir-mexico-concepcion-del-oro</t>
+  </si>
+  <si>
     <t>Domestic Violence Advocate</t>
   </si>
   <si>
-    <t>Barrier Free Living</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 60000.00/year</t>
   </si>
   <si>
-    <t>Disability, Housing Homelessness, Human Rights Civil Liberties</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5192ba488a974994bc8bb8499441abda-domestic-violence-advocate-barrier-free-living-new-york</t>
   </si>
   <si>
@@ -901,9 +1384,6 @@
     <t>https://www.idealist.org/en/nonprofit-job/948b4273cf1d40d3b06a78d713a0d7d5-executive-assistantdonor-manager-ray-of-hope-institute-haverstraw</t>
   </si>
   <si>
-    <t>Executive Director</t>
-  </si>
-  <si>
     <t>Kentucky Waterways Alliance</t>
   </si>
   <si>
@@ -922,9 +1402,6 @@
     <t>Hudson River Park Friends</t>
   </si>
   <si>
-    <t>Remote (New York)</t>
-  </si>
-  <si>
     <t>USD 225000.00 - 265000.00/year</t>
   </si>
   <si>
@@ -949,6 +1426,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/c636be9dbe7848fb99336514c5683629-executive-director-american-parkinson-disease-association-minneapolis</t>
   </si>
   <si>
+    <t>Oregon Children's Theatre</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/10d45db6d94b48f884cd0c870ee05b6e-executive-director-oregon-childrens-theatre-portland</t>
+  </si>
+  <si>
+    <t>Morales Consulting</t>
+  </si>
+  <si>
+    <t>Kansas City, Kansas</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/368e381989da42888b9c47d2851ad414-executive-director-morales-consulting-kansas-city</t>
+  </si>
+  <si>
+    <t>Sisters Transportation and Ride Share</t>
+  </si>
+  <si>
+    <t>Sisters, Oregon</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Rural Areas, Transportation, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cfe8221949845339732ce153d19e255-executive-director-sisters-transportation-and-ride-share-sisters</t>
+  </si>
+  <si>
     <t>Executive Director- Environmental Justice Focus</t>
   </si>
   <si>
@@ -970,12 +1486,57 @@
     <t>International Sign Association</t>
   </si>
   <si>
-    <t>USD 60000.00 - 65000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/9b61cf103fc74734b4d307cd0147fcd3-exhibit-and-sponsorship-coordinator-international-sign-association-alexandria</t>
   </si>
   <si>
+    <t>Facilitador/a de Proyecto Especial en Protección - Villahermosa, Tab.</t>
+  </si>
+  <si>
+    <t>World Vision México</t>
+  </si>
+  <si>
+    <t>Villahermosa, Tabasco, MX</t>
+  </si>
+  <si>
+    <t>MXN 11782.00 - 11782.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/121a641556924c8c814a68cae2ac5470-facilitadora-de-proyecto-especial-en-proteccion-villahermosa-tab-world-vision-mexico-villahermosa</t>
+  </si>
+  <si>
+    <t>Family Intervention Specialist - Memphis, TN</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/50547bdfaa5541d2a3017045377eac9c-family-intervention-specialist-memphis-tn-youth-villages-memphis</t>
+  </si>
+  <si>
+    <t>Finance &amp; Operations Lead</t>
+  </si>
+  <si>
+    <t>Women Make Movies</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Communications Access, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b234fda8bbf4854aedb168a9cae2b2c-finance-operations-lead-women-make-movies-new-york</t>
+  </si>
+  <si>
     <t>Finance Coordinator [Part-time]</t>
   </si>
   <si>
@@ -1015,9 +1576,6 @@
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 50.00 - 100.00/month</t>
   </si>
   <si>
@@ -1042,6 +1600,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/d84f85a36164455ba3451d0d6c29b75b-housing-counselor-allston-brighton-community-development-corporation-boston</t>
   </si>
   <si>
+    <t>Immigration Padilla Attorney, CDP, Queens Office</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 183000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2f48efb1a6345d79fc8f073f1e8f7f0-immigration-padilla-attorney-cdp-queens-office-brooklyn-defender-services-queens-county</t>
+  </si>
+  <si>
+    <t>IT Infrastructure Administrator</t>
+  </si>
+  <si>
+    <t>Coalition for the Homeless</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2455839c413f49d8b111168cff0ed306-it-infrastructure-administrator-coalition-for-the-homeless-new-york</t>
+  </si>
+  <si>
     <t>Lead, Direct Care Workforce Development</t>
   </si>
   <si>
@@ -1051,9 +1639,6 @@
     <t>Arlington, VA</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 100000.00 - 120000.00/year</t>
   </si>
   <si>
@@ -1063,6 +1648,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/f11a3555c8ce4f23a6f597a9ffa349f4-lead-direct-care-workforce-development-national-council-on-aging-arlington</t>
   </si>
   <si>
+    <t>Legal Operations Manager</t>
+  </si>
+  <si>
+    <t>New York International Arbitration Center, Inc. (NYIAC)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Conflict Resolution, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c059b6d48e9244f8a64d8bdc19bc18df-legal-operations-manager-new-york-international-arbitration-center-inc-nyiac-new-york</t>
+  </si>
+  <si>
+    <t>Live-In Resident Monitor</t>
+  </si>
+  <si>
+    <t>Community Family Life Services</t>
+  </si>
+  <si>
+    <t>USD 18.40/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc80c85a85e249598ee4f4462ff03043-live-in-resident-monitor-community-family-life-services-washington</t>
+  </si>
+  <si>
     <t>Local Food Access Delivery Driver</t>
   </si>
   <si>
@@ -1138,9 +1750,6 @@
     <t>Public Advocates Inc.</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 171600.00 - 200000.00/year</t>
   </si>
   <si>
@@ -1168,6 +1777,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/0f0407033ffc44c88bbf2611ec9db02c-managing-director-boston-city-singers-boston-city-singers-boston</t>
   </si>
   <si>
+    <t>Marketing &amp; Communications Director</t>
+  </si>
+  <si>
+    <t>Equality Labs</t>
+  </si>
+  <si>
+    <t>USD 97500.00 - 97500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/f365a9cbd4874cf18f658fd16d0cae58-marketing-communications-director-equality-labs-san-francisco</t>
+  </si>
+  <si>
+    <t>Mary Valle Foundation Coordinator</t>
+  </si>
+  <si>
+    <t>Ability Now Bay Area</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34fb9a2ebbba4e8ebccc35913da0dbe5-mary-valle-foundation-coordinator-ability-now-bay-area-oakland</t>
+  </si>
+  <si>
     <t>Medical Referral Coordinator II</t>
   </si>
   <si>
@@ -1183,15 +1819,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/941e5be4396e4d4b9e02a7889156ecbe-medical-referral-coordinator-ii-bread-for-the-city-washington</t>
   </si>
   <si>
+    <t>Membership Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a18bcf940db4f4d93d82d89eb1fe910-membership-manager-academy-of-american-poets-new-york</t>
+  </si>
+  <si>
+    <t>Mentor &amp; Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Asian American LEAD</t>
+  </si>
+  <si>
+    <t>USD 43000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf12e57236954f4f98002f12d1ddb140-mentor-volunteer-coordinator-asian-american-lead-washington</t>
+  </si>
+  <si>
     <t>National Executive Assistant</t>
   </si>
   <si>
     <t>After-School All-Stars</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -1201,6 +1852,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/bf0554a846894ec4acd09662ade469d1-national-executive-assistant-after-school-all-stars-los-angeles</t>
   </si>
   <si>
+    <t>National Organizing Department (NOD) Mobilizing &amp; Training Organizer</t>
+  </si>
+  <si>
+    <t>Showing Up for Racial Justice (SURJ)</t>
+  </si>
+  <si>
+    <t>USD 69000.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>Race Ethnicity, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5589db16e3da4bffa35c6b9ade7f7d59-national-organizing-department-nod-mobilizing-training-organizer-showing-up-for-racial-justice-surj-buffalo</t>
+  </si>
+  <si>
     <t>Nonpartisan Election Protection Hotline Captain</t>
   </si>
   <si>
@@ -1216,6 +1882,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/12afe66365e545d9b38db871d0448ea6-nonpartisan-election-protection-hotline-captain-promote-the-vote-detroit</t>
   </si>
   <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>SF New Deal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b86985f8a73e4c22b030e2b049ca2c73-operations-associate-sf-new-deal-san-francisco</t>
+  </si>
+  <si>
+    <t>Out of School Time (OST) Program Facilitator, Part-Time Contractor</t>
+  </si>
+  <si>
+    <t>Project Invent</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 10000.00 - 10000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dc4e819694d24403b82cd1fd4b0df7cc-out-of-school-time-ost-program-facilitator-part-time-contractor-project-invent-saint-paul</t>
+  </si>
+  <si>
+    <t>PAC Manager/Assistant Political Director</t>
+  </si>
+  <si>
+    <t>J Street</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d0d9603fd85400a8c7ac9747e0ea683-pac-managerassistant-political-director-j-street-washington</t>
+  </si>
+  <si>
     <t>Paralegal (full-time) at Law Firm Exclusively Serving Nonprofit/Tax-Exempt Organizations</t>
   </si>
   <si>
@@ -1243,6 +1948,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/6cec7efe38714988a2087782d678e3cc-part-time-development-director-family-reading-partners-carrboro</t>
   </si>
   <si>
+    <t>People Operations Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdc6b0e653f04a94a729c0ac074c3130-people-operations-manager-sf-new-deal-san-francisco</t>
+  </si>
+  <si>
     <t>Pianist</t>
   </si>
   <si>
@@ -1258,6 +1969,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/f8678cdc81764e709816b71e0e746a7c-pianist-national-dance-institute-new-york</t>
   </si>
   <si>
+    <t>Policy Counsel or Senior Policy Counsel</t>
+  </si>
+  <si>
+    <t>Americans United for Separation of Church and State</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 87822.00 - 131733.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15df6b734bca4edaa55b6d38b4112d94-policy-counsel-or-senior-policy-counsel-americans-united-for-separation-of-church-and-state-washington</t>
+  </si>
+  <si>
+    <t>Policy Fellow (Fall 2026-Fall 2028)</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Maine</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 131846.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d5288c920fa4f738b6a0c60e96df59b-policy-fellow-fall-2026-fall-2028-american-civil-liberties-union-of-maine-portland</t>
+  </si>
+  <si>
     <t>Program Associate, BioQuest</t>
   </si>
   <si>
@@ -1270,6 +2017,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/8d8fc7f6df5840f58fbe6c6420f7c369-program-associate-bioquest-rtw-foundation-new-york</t>
   </si>
   <si>
+    <t>Program Associate, Governors Public Health Alliance</t>
+  </si>
+  <si>
+    <t>Governors Action Alliance</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Civic Engagement, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/011a38cf6f84450489f1fca441e87c6c-program-associate-governors-public-health-alliance-governors-action-alliance-washington</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
@@ -1279,15 +2041,21 @@
     <t>Culver City, California</t>
   </si>
   <si>
-    <t>USD 24.00 - 26.00/hour</t>
-  </si>
-  <si>
     <t>Children Youth</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/efe386f51879474e82c12c7785b2dbb2-program-coordinator-baby2baby-culver-city</t>
   </si>
   <si>
+    <t>Program Coordinator- Strategic Partnerships &amp; Policy (FSA)</t>
+  </si>
+  <si>
+    <t>USD 35.51 - 35.51/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fdc57668df34cb6a9fb084ecd38e80b-program-coordinator-strategic-partnerships-policy-fsa-safe-sound-san-francisco</t>
+  </si>
+  <si>
     <t>Program Director</t>
   </si>
   <si>
@@ -1297,15 +2065,18 @@
     <t>Kings County, New York</t>
   </si>
   <si>
-    <t>USD 95000.00 - 105000.00/year</t>
-  </si>
-  <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/240c35b8715c45fcbda6b8e6becb194e-program-director-partnership-with-children-kings-county</t>
   </si>
   <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7e49e49e6e142e59f0ed29ef3035b25-program-manager-catholic-charities-archdiocese-of-ny-new-york</t>
+  </si>
+  <si>
     <t>Program Support Specialist</t>
   </si>
   <si>
@@ -1321,6 +2092,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/7b0912efc029423e8fbb9193e178e8de-program-support-specialist-the-ark-chicago</t>
   </si>
   <si>
+    <t>Project Manager - Mississippi</t>
+  </si>
+  <si>
+    <t>Alliance for Affordable Energy</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Consumer Protection</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af02723b703f42e48580e86b867171fc-project-manager-mississippi-alliance-for-affordable-energy-new-orleans</t>
+  </si>
+  <si>
+    <t>Project Manager - Outreach &amp; Diversion</t>
+  </si>
+  <si>
+    <t>Partners for HOME</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 73268.00 - 84150.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63faf19916a94f7c9bf979356881ff80-project-manager-outreach-diversion-partners-for-home-atlanta</t>
+  </si>
+  <si>
+    <t>Project Receptionist: Domestic Violence Project</t>
+  </si>
+  <si>
+    <t>Counsel for Justice</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Victim Support, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a75018787e241b496cebb0cfbc90743-project-receptionist-domestic-violence-project-counsel-for-justice-los-angeles</t>
+  </si>
+  <si>
     <t>Recruitment Manager</t>
   </si>
   <si>
@@ -1348,6 +2161,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/2764bcc6abc64fbf88b3c7d040f90630-regional-campaign-manager-riders-alliance-new-york</t>
   </si>
   <si>
+    <t>Regional Campaign Manager, Northern California</t>
+  </si>
+  <si>
+    <t>Greenlight America</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72f64d09eea4494fb2df41d88964c3ad-regional-campaign-manager-northern-california-greenlight-america-washington</t>
+  </si>
+  <si>
+    <t>Remote Community Organizer - Phonebanking</t>
+  </si>
+  <si>
+    <t>GroundWorks Campaigns</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6eb7fc7f6fec4ba5a6918f6d6d57ec8b-remote-community-organizer-phonebanking-groundworks-campaigns-berkeley</t>
+  </si>
+  <si>
+    <t>Repair &amp; Refurbish Mechanic</t>
+  </si>
+  <si>
+    <t>Bikes Not Bombs</t>
+  </si>
+  <si>
+    <t>Jamaica Plain, MA</t>
+  </si>
+  <si>
+    <t>USD 19.23 - 24.04/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1958580103b54a3090979f85a2e1eeee-repair-refurbish-mechanic-bikes-not-bombs-jamaica-plain</t>
+  </si>
+  <si>
+    <t>Research Manager or Sr. Research Manager</t>
+  </si>
+  <si>
+    <t>USD 82335.00 - 109777.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b6cfcd0aeb44789b7262a2146fe4098-research-manager-or-sr-research-manager-americans-united-for-separation-of-church-and-state-washington</t>
+  </si>
+  <si>
+    <t>Scholarship Administration Coordinator</t>
+  </si>
+  <si>
+    <t>University of North Carolina - Charlotte</t>
+  </si>
+  <si>
+    <t>Charlotte, North Carolina</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a9c0901b585a42c5a9a17b400318b0d0-scholarship-administration-coordinator-university-of-north-carolina-charlotte-charlotte</t>
+  </si>
+  <si>
     <t>Second Grade Lead Teacher (Immediate Opening)</t>
   </si>
   <si>
@@ -1360,6 +2242,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/8b0ec9dcbb194cccbbc3b0d88e3afa1d-second-grade-lead-teacher-immediate-opening-harlem-academy-new-york</t>
   </si>
   <si>
+    <t>Senior Director of Development &amp; Major Gifts</t>
+  </si>
+  <si>
+    <t>Island Senior Resources</t>
+  </si>
+  <si>
+    <t>Langley, Washington</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7491a2363aa74aa19ca03ad3e03214f0-senior-director-of-development-major-gifts-island-senior-resources-langley</t>
+  </si>
+  <si>
+    <t>Senior Dues and Data Specialist</t>
+  </si>
+  <si>
+    <t>SEIU Wisconsin Healthcare and Service Workers Stronger Together</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 76541.03 - 88148.02/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/506fb2993c0844c8b533a35481137fe9-senior-dues-and-data-specialist-seiu-wisconsin-healthcare-and-service-workers-stronger-together-madison</t>
+  </si>
+  <si>
     <t>Service Enriched Housing Super Hero</t>
   </si>
   <si>
@@ -1375,6 +2290,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/db3c4abd6bb14d4e9d7d27c6d95a72ee-service-enriched-housing-super-hero-community-housing-resource-partners-inc-denton</t>
   </si>
   <si>
+    <t>Spring, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de5ccb3ea098468b861f28baf1b755c6-service-enriched-housing-super-hero-community-housing-resource-partners-inc-spring</t>
+  </si>
+  <si>
+    <t>Social Worker</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7232a6f62d6e4bb59438d058275efea6-social-worker-barrier-free-living-new-york</t>
+  </si>
+  <si>
     <t>Special Assistant Attorney General: Civil Enforcement (3906)</t>
   </si>
   <si>
@@ -1387,21 +2323,69 @@
     <t>https://www.idealist.org/en/government-job/63e9749137674330ba61bb6b8b48594b-special-assistant-attorney-general-civil-enforcement-3906-new-york-state-office-of-the-attorney-general-new-york</t>
   </si>
   <si>
+    <t>Special Assistant Attorney General: Medicaid Fraud (3907)</t>
+  </si>
+  <si>
+    <t>Mineola, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/1f47c2cfd6514006978430c85812be97-special-assistant-attorney-general-medicaid-fraud-3907-new-york-state-office-of-the-attorney-general-mineola</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
     <t>Congregation Rodeph Sholom &amp; Rodeph Sholom School</t>
   </si>
   <si>
-    <t>USD 65000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>Religion Spirituality, Education</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/551bce29c7584e1b98726e689eee3168-staff-accountant-congregation-rodeph-sholom-rodeph-sholom-school-new-york</t>
   </si>
   <si>
+    <t>Staff Attorney/Senior Staff Attorney/ Senior Counsel</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of New Jersey</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 96000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2dc9126e153c4ea893a1c2f62e075546-staff-attorneysenior-staff-attorney-senior-counsel-american-civil-liberties-union-of-new-jersey-newark</t>
+  </si>
+  <si>
+    <t>Teaching Fellow/Teacher</t>
+  </si>
+  <si>
+    <t>City Teaching Alliance</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/059d0dfb3bc2426eaf997da6fe357e09-teaching-fellowteacher-city-teaching-alliance-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9031212b45c343b5a7c1bb40a739082a-teaching-fellowteacher-city-teaching-alliance-philadelphia</t>
+  </si>
+  <si>
+    <t>Dallas County, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e84df911c0743af87de96a34870dd78-teaching-fellowteacher-city-teaching-alliance-dallas-county</t>
+  </si>
+  <si>
+    <t>Baltimore County, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40456fd6241640168c194e9af47c3456-teaching-fellowteacher-city-teaching-alliance-baltimore-county</t>
+  </si>
+  <si>
     <t>Telehealth Coordinator</t>
   </si>
   <si>
@@ -1414,6 +2398,36 @@
     <t>https://www.idealist.org/en/job/384c1aa2c3ef4bca80893d8ccef4f273-telehealth-coordinator-remote-area-medical-rockford</t>
   </si>
   <si>
+    <t>Temporary SCOPE Administrative Assistant</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Race Ethnicity, Rural Areas, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d03ff3afabab4723a80a112bd75b587e-temporary-scope-administrative-assistant-showing-up-for-racial-justice-surj-buffalo</t>
+  </si>
+  <si>
+    <t>Tenant Rights Advocacy Specialist</t>
+  </si>
+  <si>
+    <t>Inquilinos Unidos (United Tenants)</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 32.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Urban Areas, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22b63378da374752a79f8bffbeef0263-tenant-rights-advocacy-specialist-inquilinos-unidos-united-tenants-los-angeles</t>
+  </si>
+  <si>
     <t>The Moth - Senior Manager, Global Community</t>
   </si>
   <si>
@@ -1438,6 +2452,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/c5ef4e03e6a54469af1d7b4d48200350-the-moth-vice-president-business-partnerships-the-moth-new-york</t>
   </si>
   <si>
+    <t>Therapist</t>
+  </si>
+  <si>
+    <t>Doorways</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee2cb14910af4e148c13291e5a07f47f-therapist-doorways-arlington</t>
+  </si>
+  <si>
     <t>TRABAJADOR/A SOCIAL</t>
   </si>
   <si>
@@ -1466,6 +2498,153 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/7f808df352f14e2a8c24b913e50e1d42-vice-president-of-advancement-united-through-reading-san-diego</t>
+  </si>
+  <si>
+    <t>Youth Program Coordinator</t>
+  </si>
+  <si>
+    <t>Lowell Association for the Blind</t>
+  </si>
+  <si>
+    <t>Lowell, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/637e1a31b7d846f8a4ca416dd14fece8-youth-program-coordinator-lowell-association-for-the-blind-lowell</t>
+  </si>
+  <si>
+    <t>ASSISTANT LIVESTOCK MANAGER</t>
+  </si>
+  <si>
+    <t>Glynwood Center</t>
+  </si>
+  <si>
+    <t>Cold Spring, New York</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72800329</t>
+  </si>
+  <si>
+    <t>CONSERVATION GRAZING PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Los Altos, California</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72801551</t>
+  </si>
+  <si>
+    <t>EDUCATION AND COMMUNITY GARDEN COORDINATOR</t>
+  </si>
+  <si>
+    <t>VINES</t>
+  </si>
+  <si>
+    <t>Binghamton, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72795441</t>
+  </si>
+  <si>
+    <t>FACULTY SPECIALIST</t>
+  </si>
+  <si>
+    <t>AGRICULTURAL NUTRIENT MANAGEMENT PROGRAM - University of Maryland Extension</t>
+  </si>
+  <si>
+    <t>College Park, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72802773</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72803995</t>
+  </si>
+  <si>
+    <t>FARM MANAGER</t>
+  </si>
+  <si>
+    <t>Farm Discovery at Live Earth</t>
+  </si>
+  <si>
+    <t>Watsonville, California</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72796663</t>
+  </si>
+  <si>
+    <t>LOGISTICS AND OPERATIONS COORDINATOR</t>
+  </si>
+  <si>
+    <t>HATCH</t>
+  </si>
+  <si>
+    <t>Carmel, Indiana</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72799107</t>
+  </si>
+  <si>
+    <t>NEW YORK PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Remote within two hours of Saratoga Springs, New Y</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72792997</t>
+  </si>
+  <si>
+    <t>PRODUCT AND ZERO WASTE SPECIALIST</t>
+  </si>
+  <si>
+    <t>ECO PRODUCTS - Novolex</t>
+  </si>
+  <si>
+    <t>Boulder, Colorado</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72790553</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72791775</t>
+  </si>
+  <si>
+    <t>SOUP KITCHEN LEAD</t>
+  </si>
+  <si>
+    <t>Haley House</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72797885</t>
+  </si>
+  <si>
+    <t>SR MANAGER</t>
+  </si>
+  <si>
+    <t>DAIRY CLIMATE SMART AGRICULTURE - Mars</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72794219</t>
   </si>
 </sst>
 </file>
@@ -1851,7 +3030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2108,7 +3287,7 @@
         <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
@@ -2125,13 +3304,13 @@
         <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
@@ -2148,42 +3327,42 @@
         <v>77</v>
       </c>
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
       </c>
       <c r="E13" t="s">
         <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>87</v>
@@ -2309,65 +3488,65 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
         <v>44</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>131</v>
@@ -2378,88 +3557,88 @@
         <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F24" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F26" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>151</v>
@@ -2482,79 +3661,125 @@
         <v>155</v>
       </c>
       <c r="F27" t="s">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>178</v>
+      </c>
+      <c r="F31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" t="s">
+        <v>181</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2589,6 +3814,8 @@
     <hyperlink ref="H28" r:id="rId27"/>
     <hyperlink ref="H29" r:id="rId28"/>
     <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2597,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2638,31 +3865,82 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
-        <v>178</v>
+        <v>190</v>
+      </c>
+      <c r="G2" t="s">
+        <v>191</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2671,7 +3949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2712,1336 +3990,3015 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="F2" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="F3" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="D4" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="F4" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>183</v>
+        <v>232</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="E7" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="F8" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="D9" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="F9" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="B10" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="B12" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>189</v>
       </c>
       <c r="F12" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B13" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D13" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="E13" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="F13" t="s">
-        <v>197</v>
+        <v>272</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="B14" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C14" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E14" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="E15" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="F15" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="B16" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C16" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="D16" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E16" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="F16" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B17" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E17" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="F17" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>201</v>
+        <v>293</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="F18" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="B19" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
       <c r="D19" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="E19" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>303</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="E20" t="s">
-        <v>282</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>287</v>
+        <v>189</v>
       </c>
       <c r="F21" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C22" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="D22" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E22" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="F22" t="s">
-        <v>177</v>
+        <v>314</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C23" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="D23" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E23" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="F23" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="B24" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C24" t="s">
-        <v>302</v>
+        <v>231</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E24" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="F24" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="B25" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C25" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="D25" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="E25" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="F25" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="B26" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C26" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D26" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="F26" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="B27" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C27" t="s">
-        <v>201</v>
+        <v>340</v>
       </c>
       <c r="D27" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E27" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="F27" t="s">
-        <v>177</v>
+        <v>342</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="B28" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="C28" t="s">
-        <v>230</v>
+        <v>346</v>
       </c>
       <c r="D28" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E28" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="F28" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="B29" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C29" t="s">
-        <v>327</v>
+        <v>231</v>
       </c>
       <c r="D29" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="F29" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="B30" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>357</v>
       </c>
       <c r="D30" t="s">
-        <v>333</v>
+        <v>207</v>
       </c>
       <c r="E30" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="F30" t="s">
-        <v>335</v>
+        <v>240</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="B31" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>362</v>
       </c>
       <c r="D31" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E31" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="F31" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="B32" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C32" t="s">
-        <v>344</v>
+        <v>255</v>
       </c>
       <c r="D32" t="s">
-        <v>345</v>
+        <v>207</v>
       </c>
       <c r="E32" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="F32" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B33" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C33" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="D33" t="s">
-        <v>333</v>
+        <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="F33" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="B34" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C34" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E34" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F34" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B35" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E35" t="s">
-        <v>363</v>
+        <v>189</v>
       </c>
       <c r="F35" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="B36" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C36" t="s">
-        <v>368</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E36" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="F36" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B37" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C37" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E37" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="F37" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="C38" t="s">
-        <v>380</v>
+        <v>231</v>
       </c>
       <c r="D38" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E38" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="F38" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E39" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="F39" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="C40" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E40" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="F40" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>416</v>
       </c>
       <c r="D41" t="s">
-        <v>333</v>
+        <v>207</v>
       </c>
       <c r="E41" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="F41" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B42" t="s">
-        <v>401</v>
+        <v>258</v>
       </c>
       <c r="C42" t="s">
-        <v>368</v>
+        <v>195</v>
       </c>
       <c r="D42" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E42" t="s">
-        <v>293</v>
+        <v>421</v>
       </c>
       <c r="F42" t="s">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="B43" t="s">
-        <v>404</v>
+        <v>258</v>
       </c>
       <c r="C43" t="s">
-        <v>405</v>
+        <v>195</v>
       </c>
       <c r="D43" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E43" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="F43" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="C44" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D44" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E44" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="F44" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C45" t="s">
-        <v>230</v>
+        <v>434</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>435</v>
       </c>
       <c r="E45" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="F45" t="s">
-        <v>203</v>
+        <v>437</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s">
-        <v>419</v>
+        <v>275</v>
       </c>
       <c r="C46" t="s">
-        <v>420</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E46" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="F46" t="s">
-        <v>422</v>
+        <v>277</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="B47" t="s">
-        <v>425</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>426</v>
+        <v>195</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E47" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="F47" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="B48" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="C48" t="s">
-        <v>432</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="F48" t="s">
-        <v>177</v>
+        <v>449</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="C49" t="s">
-        <v>201</v>
+        <v>453</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E49" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="F49" t="s">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>439</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="C50" t="s">
-        <v>230</v>
+        <v>457</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E50" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="F50" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>444</v>
+        <v>199</v>
       </c>
       <c r="B51" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="C51" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
       <c r="D51" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E51" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="F51" t="s">
-        <v>428</v>
+        <v>463</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>448</v>
+        <v>199</v>
       </c>
       <c r="B52" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="C52" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="D52" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E52" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="F52" t="s">
-        <v>177</v>
+        <v>468</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>453</v>
+        <v>199</v>
       </c>
       <c r="B53" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="C53" t="s">
-        <v>230</v>
+        <v>471</v>
       </c>
       <c r="D53" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E53" t="s">
-        <v>455</v>
+        <v>189</v>
       </c>
       <c r="F53" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>457</v>
+        <v>199</v>
       </c>
       <c r="B54" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>474</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E54" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="F54" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>462</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="C55" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="D55" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="E55" t="s">
-        <v>177</v>
+        <v>480</v>
       </c>
       <c r="F55" t="s">
-        <v>177</v>
+        <v>481</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C56" t="s">
-        <v>230</v>
+        <v>485</v>
       </c>
       <c r="D56" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E56" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="F56" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="B57" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="C57" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="D57" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E57" t="s">
-        <v>472</v>
+        <v>324</v>
       </c>
       <c r="F57" t="s">
-        <v>469</v>
+        <v>189</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="B58" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C58" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>435</v>
       </c>
       <c r="E58" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="F58" t="s">
-        <v>177</v>
+        <v>495</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B59" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="C59" t="s">
-        <v>201</v>
+        <v>499</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="E59" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="F59" t="s">
-        <v>482</v>
+        <v>251</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>483</v>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>502</v>
+      </c>
+      <c r="B60" t="s">
+        <v>503</v>
+      </c>
+      <c r="C60" t="s">
+        <v>231</v>
+      </c>
+      <c r="D60" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" t="s">
+        <v>504</v>
+      </c>
+      <c r="F60" t="s">
+        <v>505</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>507</v>
+      </c>
+      <c r="B61" t="s">
+        <v>508</v>
+      </c>
+      <c r="C61" t="s">
+        <v>231</v>
+      </c>
+      <c r="D61" t="s">
+        <v>270</v>
+      </c>
+      <c r="E61" t="s">
+        <v>509</v>
+      </c>
+      <c r="F61" t="s">
+        <v>510</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>512</v>
+      </c>
+      <c r="B62" t="s">
+        <v>513</v>
+      </c>
+      <c r="C62" t="s">
+        <v>514</v>
+      </c>
+      <c r="D62" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" t="s">
+        <v>515</v>
+      </c>
+      <c r="F62" t="s">
+        <v>516</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>518</v>
+      </c>
+      <c r="B63" t="s">
+        <v>519</v>
+      </c>
+      <c r="C63" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E63" t="s">
+        <v>520</v>
+      </c>
+      <c r="F63" t="s">
+        <v>521</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>523</v>
+      </c>
+      <c r="B64" t="s">
+        <v>524</v>
+      </c>
+      <c r="C64" t="s">
+        <v>357</v>
+      </c>
+      <c r="D64" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" t="s">
+        <v>525</v>
+      </c>
+      <c r="F64" t="s">
+        <v>526</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>528</v>
+      </c>
+      <c r="B65" t="s">
+        <v>529</v>
+      </c>
+      <c r="C65" t="s">
+        <v>530</v>
+      </c>
+      <c r="D65" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" t="s">
+        <v>531</v>
+      </c>
+      <c r="F65" t="s">
+        <v>532</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>534</v>
+      </c>
+      <c r="B66" t="s">
+        <v>535</v>
+      </c>
+      <c r="C66" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66" t="s">
+        <v>207</v>
+      </c>
+      <c r="E66" t="s">
+        <v>244</v>
+      </c>
+      <c r="F66" t="s">
+        <v>536</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>538</v>
+      </c>
+      <c r="B67" t="s">
+        <v>539</v>
+      </c>
+      <c r="C67" t="s">
+        <v>540</v>
+      </c>
+      <c r="D67" t="s">
+        <v>435</v>
+      </c>
+      <c r="E67" t="s">
+        <v>541</v>
+      </c>
+      <c r="F67" t="s">
+        <v>542</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>544</v>
+      </c>
+      <c r="B68" t="s">
+        <v>545</v>
+      </c>
+      <c r="C68" t="s">
+        <v>231</v>
+      </c>
+      <c r="D68" t="s">
+        <v>207</v>
+      </c>
+      <c r="E68" t="s">
+        <v>546</v>
+      </c>
+      <c r="F68" t="s">
+        <v>547</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>549</v>
+      </c>
+      <c r="B69" t="s">
+        <v>550</v>
+      </c>
+      <c r="C69" t="s">
+        <v>225</v>
+      </c>
+      <c r="D69" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" t="s">
+        <v>551</v>
+      </c>
+      <c r="F69" t="s">
+        <v>227</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>553</v>
+      </c>
+      <c r="B70" t="s">
+        <v>554</v>
+      </c>
+      <c r="C70" t="s">
+        <v>555</v>
+      </c>
+      <c r="D70" t="s">
+        <v>232</v>
+      </c>
+      <c r="E70" t="s">
+        <v>556</v>
+      </c>
+      <c r="F70" t="s">
+        <v>557</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>559</v>
+      </c>
+      <c r="B71" t="s">
+        <v>560</v>
+      </c>
+      <c r="C71" t="s">
+        <v>561</v>
+      </c>
+      <c r="D71" t="s">
+        <v>207</v>
+      </c>
+      <c r="E71" t="s">
+        <v>562</v>
+      </c>
+      <c r="F71" t="s">
+        <v>563</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>565</v>
+      </c>
+      <c r="B72" t="s">
+        <v>566</v>
+      </c>
+      <c r="C72" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72" t="s">
+        <v>567</v>
+      </c>
+      <c r="F72" t="s">
+        <v>568</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>570</v>
+      </c>
+      <c r="B73" t="s">
+        <v>571</v>
+      </c>
+      <c r="C73" t="s">
+        <v>572</v>
+      </c>
+      <c r="D73" t="s">
+        <v>207</v>
+      </c>
+      <c r="E73" t="s">
+        <v>573</v>
+      </c>
+      <c r="F73" t="s">
+        <v>574</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>576</v>
+      </c>
+      <c r="B74" t="s">
+        <v>577</v>
+      </c>
+      <c r="C74" t="s">
+        <v>249</v>
+      </c>
+      <c r="D74" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74" t="s">
+        <v>578</v>
+      </c>
+      <c r="F74" t="s">
+        <v>579</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>581</v>
+      </c>
+      <c r="B75" t="s">
+        <v>582</v>
+      </c>
+      <c r="C75" t="s">
+        <v>583</v>
+      </c>
+      <c r="D75" t="s">
+        <v>207</v>
+      </c>
+      <c r="E75" t="s">
+        <v>584</v>
+      </c>
+      <c r="F75" t="s">
+        <v>585</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>587</v>
+      </c>
+      <c r="B76" t="s">
+        <v>588</v>
+      </c>
+      <c r="C76" t="s">
+        <v>195</v>
+      </c>
+      <c r="D76" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" t="s">
+        <v>589</v>
+      </c>
+      <c r="F76" t="s">
+        <v>189</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>591</v>
+      </c>
+      <c r="B77" t="s">
+        <v>592</v>
+      </c>
+      <c r="C77" t="s">
+        <v>379</v>
+      </c>
+      <c r="D77" t="s">
+        <v>270</v>
+      </c>
+      <c r="E77" t="s">
+        <v>593</v>
+      </c>
+      <c r="F77" t="s">
+        <v>594</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>596</v>
+      </c>
+      <c r="B78" t="s">
+        <v>597</v>
+      </c>
+      <c r="C78" t="s">
+        <v>225</v>
+      </c>
+      <c r="D78" t="s">
+        <v>207</v>
+      </c>
+      <c r="E78" t="s">
+        <v>598</v>
+      </c>
+      <c r="F78" t="s">
+        <v>599</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>601</v>
+      </c>
+      <c r="B79" t="s">
+        <v>399</v>
+      </c>
+      <c r="C79" t="s">
+        <v>231</v>
+      </c>
+      <c r="D79" t="s">
+        <v>207</v>
+      </c>
+      <c r="E79" t="s">
+        <v>341</v>
+      </c>
+      <c r="F79" t="s">
+        <v>401</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>603</v>
+      </c>
+      <c r="B80" t="s">
+        <v>604</v>
+      </c>
+      <c r="C80" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" t="s">
+        <v>605</v>
+      </c>
+      <c r="F80" t="s">
+        <v>227</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>607</v>
+      </c>
+      <c r="B81" t="s">
+        <v>608</v>
+      </c>
+      <c r="C81" t="s">
+        <v>255</v>
+      </c>
+      <c r="D81" t="s">
+        <v>207</v>
+      </c>
+      <c r="E81" t="s">
+        <v>609</v>
+      </c>
+      <c r="F81" t="s">
+        <v>610</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>612</v>
+      </c>
+      <c r="B82" t="s">
+        <v>613</v>
+      </c>
+      <c r="C82" t="s">
+        <v>195</v>
+      </c>
+      <c r="D82" t="s">
+        <v>207</v>
+      </c>
+      <c r="E82" t="s">
+        <v>614</v>
+      </c>
+      <c r="F82" t="s">
+        <v>615</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>617</v>
+      </c>
+      <c r="B83" t="s">
+        <v>618</v>
+      </c>
+      <c r="C83" t="s">
+        <v>195</v>
+      </c>
+      <c r="D83" t="s">
+        <v>232</v>
+      </c>
+      <c r="E83" t="s">
+        <v>619</v>
+      </c>
+      <c r="F83" t="s">
+        <v>620</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>622</v>
+      </c>
+      <c r="B84" t="s">
+        <v>623</v>
+      </c>
+      <c r="C84" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" t="s">
+        <v>207</v>
+      </c>
+      <c r="E84" t="s">
+        <v>515</v>
+      </c>
+      <c r="F84" t="s">
+        <v>526</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>625</v>
+      </c>
+      <c r="B85" t="s">
+        <v>626</v>
+      </c>
+      <c r="C85" t="s">
+        <v>627</v>
+      </c>
+      <c r="D85" t="s">
+        <v>232</v>
+      </c>
+      <c r="E85" t="s">
+        <v>628</v>
+      </c>
+      <c r="F85" t="s">
+        <v>320</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>630</v>
+      </c>
+      <c r="B86" t="s">
+        <v>631</v>
+      </c>
+      <c r="C86" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" t="s">
+        <v>207</v>
+      </c>
+      <c r="E86" t="s">
+        <v>632</v>
+      </c>
+      <c r="F86" t="s">
+        <v>633</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>635</v>
+      </c>
+      <c r="B87" t="s">
+        <v>636</v>
+      </c>
+      <c r="C87" t="s">
+        <v>572</v>
+      </c>
+      <c r="D87" t="s">
+        <v>207</v>
+      </c>
+      <c r="E87" t="s">
+        <v>454</v>
+      </c>
+      <c r="F87" t="s">
+        <v>574</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>638</v>
+      </c>
+      <c r="B88" t="s">
+        <v>639</v>
+      </c>
+      <c r="C88" t="s">
+        <v>640</v>
+      </c>
+      <c r="D88" t="s">
+        <v>270</v>
+      </c>
+      <c r="E88" t="s">
+        <v>641</v>
+      </c>
+      <c r="F88" t="s">
+        <v>642</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>644</v>
+      </c>
+      <c r="B89" t="s">
+        <v>623</v>
+      </c>
+      <c r="C89" t="s">
+        <v>249</v>
+      </c>
+      <c r="D89" t="s">
+        <v>207</v>
+      </c>
+      <c r="E89" t="s">
+        <v>458</v>
+      </c>
+      <c r="F89" t="s">
+        <v>526</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>646</v>
+      </c>
+      <c r="B90" t="s">
+        <v>647</v>
+      </c>
+      <c r="C90" t="s">
+        <v>231</v>
+      </c>
+      <c r="D90" t="s">
+        <v>270</v>
+      </c>
+      <c r="E90" t="s">
+        <v>648</v>
+      </c>
+      <c r="F90" t="s">
+        <v>649</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>651</v>
+      </c>
+      <c r="B91" t="s">
+        <v>652</v>
+      </c>
+      <c r="C91" t="s">
+        <v>653</v>
+      </c>
+      <c r="D91" t="s">
+        <v>207</v>
+      </c>
+      <c r="E91" t="s">
+        <v>654</v>
+      </c>
+      <c r="F91" t="s">
+        <v>655</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>657</v>
+      </c>
+      <c r="B92" t="s">
+        <v>658</v>
+      </c>
+      <c r="C92" t="s">
+        <v>659</v>
+      </c>
+      <c r="D92" t="s">
+        <v>435</v>
+      </c>
+      <c r="E92" t="s">
+        <v>660</v>
+      </c>
+      <c r="F92" t="s">
+        <v>661</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>663</v>
+      </c>
+      <c r="B93" t="s">
+        <v>664</v>
+      </c>
+      <c r="C93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D93" t="s">
+        <v>207</v>
+      </c>
+      <c r="E93" t="s">
+        <v>665</v>
+      </c>
+      <c r="F93" t="s">
+        <v>260</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>667</v>
+      </c>
+      <c r="B94" t="s">
+        <v>668</v>
+      </c>
+      <c r="C94" t="s">
+        <v>195</v>
+      </c>
+      <c r="D94" t="s">
+        <v>207</v>
+      </c>
+      <c r="E94" t="s">
+        <v>669</v>
+      </c>
+      <c r="F94" t="s">
+        <v>670</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>672</v>
+      </c>
+      <c r="B95" t="s">
+        <v>673</v>
+      </c>
+      <c r="C95" t="s">
+        <v>674</v>
+      </c>
+      <c r="D95" t="s">
+        <v>207</v>
+      </c>
+      <c r="E95" t="s">
+        <v>288</v>
+      </c>
+      <c r="F95" t="s">
+        <v>675</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>677</v>
+      </c>
+      <c r="B96" t="s">
+        <v>248</v>
+      </c>
+      <c r="C96" t="s">
+        <v>249</v>
+      </c>
+      <c r="D96" t="s">
+        <v>435</v>
+      </c>
+      <c r="E96" t="s">
+        <v>678</v>
+      </c>
+      <c r="F96" t="s">
+        <v>251</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>680</v>
+      </c>
+      <c r="B97" t="s">
+        <v>681</v>
+      </c>
+      <c r="C97" t="s">
+        <v>682</v>
+      </c>
+      <c r="D97" t="s">
+        <v>207</v>
+      </c>
+      <c r="E97" t="s">
+        <v>475</v>
+      </c>
+      <c r="F97" t="s">
+        <v>320</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>684</v>
+      </c>
+      <c r="B98" t="s">
+        <v>243</v>
+      </c>
+      <c r="C98" t="s">
+        <v>231</v>
+      </c>
+      <c r="D98" t="s">
+        <v>207</v>
+      </c>
+      <c r="E98" t="s">
+        <v>685</v>
+      </c>
+      <c r="F98" t="s">
+        <v>245</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>687</v>
+      </c>
+      <c r="B99" t="s">
+        <v>688</v>
+      </c>
+      <c r="C99" t="s">
+        <v>689</v>
+      </c>
+      <c r="D99" t="s">
+        <v>207</v>
+      </c>
+      <c r="E99" t="s">
+        <v>690</v>
+      </c>
+      <c r="F99" t="s">
+        <v>189</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>692</v>
+      </c>
+      <c r="B100" t="s">
+        <v>693</v>
+      </c>
+      <c r="C100" t="s">
+        <v>340</v>
+      </c>
+      <c r="D100" t="s">
+        <v>207</v>
+      </c>
+      <c r="E100" t="s">
+        <v>324</v>
+      </c>
+      <c r="F100" t="s">
+        <v>694</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>696</v>
+      </c>
+      <c r="B101" t="s">
+        <v>697</v>
+      </c>
+      <c r="C101" t="s">
+        <v>698</v>
+      </c>
+      <c r="D101" t="s">
+        <v>207</v>
+      </c>
+      <c r="E101" t="s">
+        <v>699</v>
+      </c>
+      <c r="F101" t="s">
+        <v>536</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>701</v>
+      </c>
+      <c r="B102" t="s">
+        <v>702</v>
+      </c>
+      <c r="C102" t="s">
+        <v>255</v>
+      </c>
+      <c r="D102" t="s">
+        <v>207</v>
+      </c>
+      <c r="E102" t="s">
+        <v>703</v>
+      </c>
+      <c r="F102" t="s">
+        <v>704</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>706</v>
+      </c>
+      <c r="B103" t="s">
+        <v>707</v>
+      </c>
+      <c r="C103" t="s">
+        <v>195</v>
+      </c>
+      <c r="D103" t="s">
+        <v>207</v>
+      </c>
+      <c r="E103" t="s">
+        <v>708</v>
+      </c>
+      <c r="F103" t="s">
+        <v>468</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>710</v>
+      </c>
+      <c r="B104" t="s">
+        <v>711</v>
+      </c>
+      <c r="C104" t="s">
+        <v>231</v>
+      </c>
+      <c r="D104" t="s">
+        <v>207</v>
+      </c>
+      <c r="E104" t="s">
+        <v>712</v>
+      </c>
+      <c r="F104" t="s">
+        <v>713</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>715</v>
+      </c>
+      <c r="B105" t="s">
+        <v>716</v>
+      </c>
+      <c r="C105" t="s">
+        <v>717</v>
+      </c>
+      <c r="D105" t="s">
+        <v>207</v>
+      </c>
+      <c r="E105" t="s">
+        <v>718</v>
+      </c>
+      <c r="F105" t="s">
+        <v>719</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>721</v>
+      </c>
+      <c r="B106" t="s">
+        <v>722</v>
+      </c>
+      <c r="C106" t="s">
+        <v>717</v>
+      </c>
+      <c r="D106" t="s">
+        <v>239</v>
+      </c>
+      <c r="E106" t="s">
+        <v>619</v>
+      </c>
+      <c r="F106" t="s">
+        <v>723</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>725</v>
+      </c>
+      <c r="B107" t="s">
+        <v>726</v>
+      </c>
+      <c r="C107" t="s">
+        <v>727</v>
+      </c>
+      <c r="D107" t="s">
+        <v>207</v>
+      </c>
+      <c r="E107" t="s">
+        <v>728</v>
+      </c>
+      <c r="F107" t="s">
+        <v>729</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>731</v>
+      </c>
+      <c r="B108" t="s">
+        <v>652</v>
+      </c>
+      <c r="C108" t="s">
+        <v>653</v>
+      </c>
+      <c r="D108" t="s">
+        <v>207</v>
+      </c>
+      <c r="E108" t="s">
+        <v>732</v>
+      </c>
+      <c r="F108" t="s">
+        <v>655</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>734</v>
+      </c>
+      <c r="B109" t="s">
+        <v>735</v>
+      </c>
+      <c r="C109" t="s">
+        <v>736</v>
+      </c>
+      <c r="D109" t="s">
+        <v>207</v>
+      </c>
+      <c r="E109" t="s">
+        <v>189</v>
+      </c>
+      <c r="F109" t="s">
+        <v>189</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>738</v>
+      </c>
+      <c r="B110" t="s">
+        <v>739</v>
+      </c>
+      <c r="C110" t="s">
+        <v>231</v>
+      </c>
+      <c r="D110" t="s">
+        <v>207</v>
+      </c>
+      <c r="E110" t="s">
+        <v>740</v>
+      </c>
+      <c r="F110" t="s">
+        <v>320</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>742</v>
+      </c>
+      <c r="B111" t="s">
+        <v>743</v>
+      </c>
+      <c r="C111" t="s">
+        <v>744</v>
+      </c>
+      <c r="D111" t="s">
+        <v>207</v>
+      </c>
+      <c r="E111" t="s">
+        <v>745</v>
+      </c>
+      <c r="F111" t="s">
+        <v>746</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>748</v>
+      </c>
+      <c r="B112" t="s">
+        <v>749</v>
+      </c>
+      <c r="C112" t="s">
+        <v>750</v>
+      </c>
+      <c r="D112" t="s">
+        <v>207</v>
+      </c>
+      <c r="E112" t="s">
+        <v>751</v>
+      </c>
+      <c r="F112" t="s">
+        <v>189</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>753</v>
+      </c>
+      <c r="B113" t="s">
+        <v>754</v>
+      </c>
+      <c r="C113" t="s">
+        <v>755</v>
+      </c>
+      <c r="D113" t="s">
+        <v>270</v>
+      </c>
+      <c r="E113" t="s">
+        <v>756</v>
+      </c>
+      <c r="F113" t="s">
+        <v>189</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>753</v>
+      </c>
+      <c r="B114" t="s">
+        <v>754</v>
+      </c>
+      <c r="C114" t="s">
+        <v>758</v>
+      </c>
+      <c r="D114" t="s">
+        <v>270</v>
+      </c>
+      <c r="E114" t="s">
+        <v>759</v>
+      </c>
+      <c r="F114" t="s">
+        <v>760</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>762</v>
+      </c>
+      <c r="B115" t="s">
+        <v>275</v>
+      </c>
+      <c r="C115" t="s">
+        <v>231</v>
+      </c>
+      <c r="D115" t="s">
+        <v>207</v>
+      </c>
+      <c r="E115" t="s">
+        <v>763</v>
+      </c>
+      <c r="F115" t="s">
+        <v>277</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>765</v>
+      </c>
+      <c r="B116" t="s">
+        <v>766</v>
+      </c>
+      <c r="C116" t="s">
+        <v>231</v>
+      </c>
+      <c r="D116" t="s">
+        <v>207</v>
+      </c>
+      <c r="E116" t="s">
+        <v>767</v>
+      </c>
+      <c r="F116" t="s">
+        <v>189</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>769</v>
+      </c>
+      <c r="B117" t="s">
+        <v>766</v>
+      </c>
+      <c r="C117" t="s">
+        <v>770</v>
+      </c>
+      <c r="D117" t="s">
+        <v>207</v>
+      </c>
+      <c r="E117" t="s">
+        <v>767</v>
+      </c>
+      <c r="F117" t="s">
+        <v>189</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>772</v>
+      </c>
+      <c r="B118" t="s">
+        <v>773</v>
+      </c>
+      <c r="C118" t="s">
+        <v>231</v>
+      </c>
+      <c r="D118" t="s">
+        <v>207</v>
+      </c>
+      <c r="E118" t="s">
+        <v>685</v>
+      </c>
+      <c r="F118" t="s">
+        <v>774</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>776</v>
+      </c>
+      <c r="B119" t="s">
+        <v>777</v>
+      </c>
+      <c r="C119" t="s">
+        <v>778</v>
+      </c>
+      <c r="D119" t="s">
+        <v>207</v>
+      </c>
+      <c r="E119" t="s">
+        <v>779</v>
+      </c>
+      <c r="F119" t="s">
+        <v>661</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>781</v>
+      </c>
+      <c r="B120" t="s">
+        <v>782</v>
+      </c>
+      <c r="C120" t="s">
+        <v>225</v>
+      </c>
+      <c r="D120" t="s">
+        <v>207</v>
+      </c>
+      <c r="E120" t="s">
+        <v>783</v>
+      </c>
+      <c r="F120" t="s">
+        <v>227</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>781</v>
+      </c>
+      <c r="B121" t="s">
+        <v>782</v>
+      </c>
+      <c r="C121" t="s">
+        <v>572</v>
+      </c>
+      <c r="D121" t="s">
+        <v>207</v>
+      </c>
+      <c r="E121" t="s">
+        <v>783</v>
+      </c>
+      <c r="F121" t="s">
+        <v>227</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>781</v>
+      </c>
+      <c r="B122" t="s">
+        <v>782</v>
+      </c>
+      <c r="C122" t="s">
+        <v>786</v>
+      </c>
+      <c r="D122" t="s">
+        <v>207</v>
+      </c>
+      <c r="E122" t="s">
+        <v>783</v>
+      </c>
+      <c r="F122" t="s">
+        <v>227</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>781</v>
+      </c>
+      <c r="B123" t="s">
+        <v>782</v>
+      </c>
+      <c r="C123" t="s">
+        <v>788</v>
+      </c>
+      <c r="D123" t="s">
+        <v>207</v>
+      </c>
+      <c r="E123" t="s">
+        <v>783</v>
+      </c>
+      <c r="F123" t="s">
+        <v>227</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>790</v>
+      </c>
+      <c r="B124" t="s">
+        <v>791</v>
+      </c>
+      <c r="C124" t="s">
+        <v>792</v>
+      </c>
+      <c r="D124" t="s">
+        <v>207</v>
+      </c>
+      <c r="E124" t="s">
+        <v>189</v>
+      </c>
+      <c r="F124" t="s">
+        <v>189</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>794</v>
+      </c>
+      <c r="B125" t="s">
+        <v>613</v>
+      </c>
+      <c r="C125" t="s">
+        <v>195</v>
+      </c>
+      <c r="D125" t="s">
+        <v>239</v>
+      </c>
+      <c r="E125" t="s">
+        <v>795</v>
+      </c>
+      <c r="F125" t="s">
+        <v>796</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>798</v>
+      </c>
+      <c r="B126" t="s">
+        <v>799</v>
+      </c>
+      <c r="C126" t="s">
+        <v>800</v>
+      </c>
+      <c r="D126" t="s">
+        <v>207</v>
+      </c>
+      <c r="E126" t="s">
+        <v>801</v>
+      </c>
+      <c r="F126" t="s">
+        <v>802</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>804</v>
+      </c>
+      <c r="B127" t="s">
+        <v>805</v>
+      </c>
+      <c r="C127" t="s">
+        <v>231</v>
+      </c>
+      <c r="D127" t="s">
+        <v>207</v>
+      </c>
+      <c r="E127" t="s">
+        <v>806</v>
+      </c>
+      <c r="F127" t="s">
+        <v>807</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>809</v>
+      </c>
+      <c r="B128" t="s">
+        <v>805</v>
+      </c>
+      <c r="C128" t="s">
+        <v>231</v>
+      </c>
+      <c r="D128" t="s">
+        <v>207</v>
+      </c>
+      <c r="E128" t="s">
+        <v>810</v>
+      </c>
+      <c r="F128" t="s">
+        <v>807</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>812</v>
+      </c>
+      <c r="B129" t="s">
+        <v>813</v>
+      </c>
+      <c r="C129" t="s">
+        <v>814</v>
+      </c>
+      <c r="D129" t="s">
+        <v>207</v>
+      </c>
+      <c r="E129" t="s">
+        <v>815</v>
+      </c>
+      <c r="F129" t="s">
+        <v>816</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>818</v>
+      </c>
+      <c r="B130" t="s">
+        <v>819</v>
+      </c>
+      <c r="C130" t="s">
+        <v>820</v>
+      </c>
+      <c r="D130" t="s">
+        <v>207</v>
+      </c>
+      <c r="E130" t="s">
+        <v>821</v>
+      </c>
+      <c r="F130" t="s">
+        <v>189</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>823</v>
+      </c>
+      <c r="B131" t="s">
+        <v>824</v>
+      </c>
+      <c r="C131" t="s">
+        <v>195</v>
+      </c>
+      <c r="D131" t="s">
+        <v>207</v>
+      </c>
+      <c r="E131" t="s">
+        <v>825</v>
+      </c>
+      <c r="F131" t="s">
+        <v>826</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>828</v>
+      </c>
+      <c r="B132" t="s">
+        <v>829</v>
+      </c>
+      <c r="C132" t="s">
+        <v>830</v>
+      </c>
+      <c r="D132" t="s">
+        <v>270</v>
+      </c>
+      <c r="E132" t="s">
+        <v>831</v>
+      </c>
+      <c r="F132" t="s">
+        <v>832</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -4105,6 +7062,79 @@
     <hyperlink ref="H57" r:id="rId56"/>
     <hyperlink ref="H58" r:id="rId57"/>
     <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4113,7 +7143,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4152,8 +7182,301 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C2" t="s">
+        <v>836</v>
+      </c>
+      <c r="D2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
+        <v>837</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" t="s">
+        <v>840</v>
+      </c>
+      <c r="D3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" t="s">
+        <v>837</v>
+      </c>
+      <c r="G3" t="s">
+        <v>841</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>843</v>
+      </c>
+      <c r="B4" t="s">
+        <v>844</v>
+      </c>
+      <c r="C4" t="s">
+        <v>845</v>
+      </c>
+      <c r="D4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" t="s">
+        <v>837</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>847</v>
+      </c>
+      <c r="B5" t="s">
+        <v>848</v>
+      </c>
+      <c r="C5" t="s">
+        <v>849</v>
+      </c>
+      <c r="D5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" t="s">
+        <v>837</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>847</v>
+      </c>
+      <c r="B6" t="s">
+        <v>848</v>
+      </c>
+      <c r="C6" t="s">
+        <v>849</v>
+      </c>
+      <c r="D6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" t="s">
+        <v>837</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B7" t="s">
+        <v>853</v>
+      </c>
+      <c r="C7" t="s">
+        <v>854</v>
+      </c>
+      <c r="D7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" t="s">
+        <v>837</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>856</v>
+      </c>
+      <c r="B8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C8" t="s">
+        <v>858</v>
+      </c>
+      <c r="D8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" t="s">
+        <v>837</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>860</v>
+      </c>
+      <c r="B9" t="s">
+        <v>861</v>
+      </c>
+      <c r="C9" t="s">
+        <v>862</v>
+      </c>
+      <c r="D9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" t="s">
+        <v>863</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>865</v>
+      </c>
+      <c r="B10" t="s">
+        <v>866</v>
+      </c>
+      <c r="C10" t="s">
+        <v>867</v>
+      </c>
+      <c r="D10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10" t="s">
+        <v>868</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>865</v>
+      </c>
+      <c r="B11" t="s">
+        <v>866</v>
+      </c>
+      <c r="C11" t="s">
+        <v>867</v>
+      </c>
+      <c r="D11" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" t="s">
+        <v>868</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B12" t="s">
+        <v>872</v>
+      </c>
+      <c r="C12" t="s">
+        <v>357</v>
+      </c>
+      <c r="D12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F12" t="s">
+        <v>837</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>874</v>
+      </c>
+      <c r="B13" t="s">
+        <v>875</v>
+      </c>
+      <c r="C13" t="s">
+        <v>346</v>
+      </c>
+      <c r="D13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" t="s">
+        <v>863</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-01.xlsx
+++ b/docs/xlsx/jobs-2026-09-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="884">
   <si>
     <t>Title</t>
   </si>
@@ -871,6 +871,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/0cda03142a1f40508042899f1a90c326-bilingual-farmworker-advocacy-network-manager-farmworker-advocacy-network-raleigh</t>
   </si>
   <si>
+    <t>Bilingual PT Farmworker Advocacy Network Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0cda03142a1f40508042899f1a90c326-bilingual-pt-farmworker-advocacy-network-manager-farmworker-advocacy-network-raleigh</t>
+  </si>
+  <si>
     <t>Bilingual Web Content &amp; Parent Support Coordinator</t>
   </si>
   <si>
@@ -1012,6 +1018,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/e60ec889d5c34a4b8021e681be1638c1-communications-and-community-coordinator-st-matthews-lutheran-church-renton-wa-renton</t>
   </si>
   <si>
+    <t>Communications and Marketing Director</t>
+  </si>
+  <si>
+    <t>Equality Labs</t>
+  </si>
+  <si>
+    <t>USD 97500.00 - 97500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/f365a9cbd4874cf18f658fd16d0cae58-communications-and-marketing-director-equality-labs-san-francisco</t>
+  </si>
+  <si>
     <t>Community &amp; Children’s Engagement Manager</t>
   </si>
   <si>
@@ -1465,6 +1483,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/4cfe8221949845339732ce153d19e255-executive-director-sisters-transportation-and-ride-share-sisters</t>
   </si>
   <si>
+    <t>Advocates for Immigrant Rights &amp; Reconciliation (AIRR)</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/368e381989da42888b9c47d2851ad414-executive-director-advocates-for-immigrant-rights-reconciliation-airr-kansas-city</t>
+  </si>
+  <si>
     <t>Executive Director- Environmental Justice Focus</t>
   </si>
   <si>
@@ -1778,12 +1805,6 @@
   </si>
   <si>
     <t>Marketing &amp; Communications Director</t>
-  </si>
-  <si>
-    <t>Equality Labs</t>
-  </si>
-  <si>
-    <t>USD 97500.00 - 97500.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/business-job/f365a9cbd4874cf18f658fd16d0cae58-marketing-communications-director-equality-labs-san-francisco</t>
@@ -3949,7 +3970,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4315,42 +4336,42 @@
         <v>285</v>
       </c>
       <c r="B16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" t="s">
+        <v>282</v>
+      </c>
+      <c r="F16" t="s">
+        <v>283</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="C16" t="s">
-        <v>287</v>
-      </c>
-      <c r="D16" t="s">
-        <v>207</v>
-      </c>
-      <c r="E16" t="s">
-        <v>288</v>
-      </c>
-      <c r="F16" t="s">
-        <v>289</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C17" t="s">
+        <v>289</v>
+      </c>
+      <c r="D17" t="s">
+        <v>207</v>
+      </c>
+      <c r="E17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F17" t="s">
         <v>291</v>
-      </c>
-      <c r="D17" t="s">
-        <v>207</v>
-      </c>
-      <c r="E17" t="s">
-        <v>288</v>
-      </c>
-      <c r="F17" t="s">
-        <v>289</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>292</v>
@@ -4358,10 +4379,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
         <v>293</v>
@@ -4370,10 +4391,10 @@
         <v>207</v>
       </c>
       <c r="E18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>294</v>
@@ -4381,677 +4402,677 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>287</v>
+      </c>
+      <c r="B19" t="s">
+        <v>288</v>
+      </c>
+      <c r="C19" t="s">
         <v>295</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E19" t="s">
+        <v>290</v>
+      </c>
+      <c r="F19" t="s">
+        <v>291</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="C19" t="s">
-        <v>297</v>
-      </c>
-      <c r="D19" t="s">
-        <v>270</v>
-      </c>
-      <c r="E19" t="s">
-        <v>298</v>
-      </c>
-      <c r="F19" t="s">
-        <v>299</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B20" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D20" t="s">
         <v>270</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>300</v>
       </c>
       <c r="F20" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B21" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C21" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D21" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="E21" t="s">
         <v>189</v>
       </c>
       <c r="F21" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>308</v>
+      </c>
+      <c r="B22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C22" t="s">
+        <v>310</v>
+      </c>
+      <c r="D22" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" t="s">
         <v>311</v>
       </c>
-      <c r="B22" t="s">
+      <c r="H22" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="C22" t="s">
-        <v>231</v>
-      </c>
-      <c r="D22" t="s">
-        <v>207</v>
-      </c>
-      <c r="E22" t="s">
-        <v>313</v>
-      </c>
-      <c r="F22" t="s">
-        <v>314</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" t="s">
+        <v>314</v>
+      </c>
+      <c r="C23" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" t="s">
+        <v>207</v>
+      </c>
+      <c r="E23" t="s">
+        <v>315</v>
+      </c>
+      <c r="F23" t="s">
         <v>316</v>
       </c>
-      <c r="B23" t="s">
+      <c r="H23" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="C23" t="s">
-        <v>318</v>
-      </c>
-      <c r="D23" t="s">
-        <v>207</v>
-      </c>
-      <c r="E23" t="s">
-        <v>319</v>
-      </c>
-      <c r="F23" t="s">
-        <v>320</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" t="s">
+        <v>320</v>
+      </c>
+      <c r="D24" t="s">
+        <v>207</v>
+      </c>
+      <c r="E24" t="s">
+        <v>321</v>
+      </c>
+      <c r="F24" t="s">
         <v>322</v>
       </c>
-      <c r="B24" t="s">
+      <c r="H24" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="C24" t="s">
-        <v>231</v>
-      </c>
-      <c r="D24" t="s">
-        <v>207</v>
-      </c>
-      <c r="E24" t="s">
-        <v>324</v>
-      </c>
-      <c r="F24" t="s">
-        <v>314</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" t="s">
+        <v>231</v>
+      </c>
+      <c r="D25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25" t="s">
         <v>326</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
+        <v>316</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C25" t="s">
-        <v>328</v>
-      </c>
-      <c r="D25" t="s">
-        <v>270</v>
-      </c>
-      <c r="E25" t="s">
-        <v>329</v>
-      </c>
-      <c r="F25" t="s">
-        <v>330</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" t="s">
+        <v>330</v>
+      </c>
+      <c r="D26" t="s">
+        <v>270</v>
+      </c>
+      <c r="E26" t="s">
+        <v>331</v>
+      </c>
+      <c r="F26" t="s">
         <v>332</v>
       </c>
-      <c r="B26" t="s">
+      <c r="H26" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="C26" t="s">
-        <v>334</v>
-      </c>
-      <c r="D26" t="s">
-        <v>207</v>
-      </c>
-      <c r="E26" t="s">
-        <v>335</v>
-      </c>
-      <c r="F26" t="s">
-        <v>336</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B27" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C27" t="s">
-        <v>340</v>
+        <v>195</v>
       </c>
       <c r="D27" t="s">
         <v>207</v>
       </c>
       <c r="E27" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F27" t="s">
-        <v>342</v>
+        <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C28" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D28" t="s">
         <v>207</v>
       </c>
       <c r="E28" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F28" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B29" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C29" t="s">
-        <v>231</v>
+        <v>346</v>
       </c>
       <c r="D29" t="s">
         <v>207</v>
       </c>
       <c r="E29" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F29" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>350</v>
+      </c>
+      <c r="B30" t="s">
+        <v>351</v>
+      </c>
+      <c r="C30" t="s">
+        <v>352</v>
+      </c>
+      <c r="D30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E30" t="s">
+        <v>353</v>
+      </c>
+      <c r="F30" t="s">
+        <v>354</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="B30" t="s">
-        <v>356</v>
-      </c>
-      <c r="C30" t="s">
-        <v>357</v>
-      </c>
-      <c r="D30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" t="s">
-        <v>358</v>
-      </c>
-      <c r="F30" t="s">
-        <v>240</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>356</v>
+      </c>
+      <c r="B31" t="s">
+        <v>357</v>
+      </c>
+      <c r="C31" t="s">
+        <v>231</v>
+      </c>
+      <c r="D31" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" t="s">
+        <v>358</v>
+      </c>
+      <c r="F31" t="s">
+        <v>359</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B31" t="s">
-        <v>361</v>
-      </c>
-      <c r="C31" t="s">
-        <v>362</v>
-      </c>
-      <c r="D31" t="s">
-        <v>207</v>
-      </c>
-      <c r="E31" t="s">
-        <v>363</v>
-      </c>
-      <c r="F31" t="s">
-        <v>364</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B32" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C32" t="s">
-        <v>255</v>
+        <v>363</v>
       </c>
       <c r="D32" t="s">
         <v>207</v>
       </c>
       <c r="E32" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F32" t="s">
-        <v>369</v>
+        <v>240</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>366</v>
+      </c>
+      <c r="B33" t="s">
+        <v>367</v>
+      </c>
+      <c r="C33" t="s">
+        <v>368</v>
+      </c>
+      <c r="D33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" t="s">
+        <v>369</v>
+      </c>
+      <c r="F33" t="s">
+        <v>370</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="B33" t="s">
-        <v>372</v>
-      </c>
-      <c r="C33" t="s">
-        <v>373</v>
-      </c>
-      <c r="D33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E33" t="s">
-        <v>374</v>
-      </c>
-      <c r="F33" t="s">
-        <v>375</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C34" t="s">
-        <v>379</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s">
         <v>207</v>
       </c>
       <c r="E34" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="F34" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B35" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C35" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D35" t="s">
         <v>207</v>
       </c>
       <c r="E35" t="s">
-        <v>189</v>
+        <v>380</v>
       </c>
       <c r="F35" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>383</v>
+      </c>
+      <c r="B36" t="s">
+        <v>384</v>
+      </c>
+      <c r="C36" t="s">
+        <v>385</v>
+      </c>
+      <c r="D36" t="s">
+        <v>207</v>
+      </c>
+      <c r="E36" t="s">
+        <v>386</v>
+      </c>
+      <c r="F36" t="s">
+        <v>387</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="B36" t="s">
-        <v>389</v>
-      </c>
-      <c r="C36" t="s">
-        <v>225</v>
-      </c>
-      <c r="D36" t="s">
-        <v>207</v>
-      </c>
-      <c r="E36" t="s">
-        <v>390</v>
-      </c>
-      <c r="F36" t="s">
-        <v>391</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>389</v>
+      </c>
+      <c r="B37" t="s">
+        <v>390</v>
+      </c>
+      <c r="C37" t="s">
+        <v>391</v>
+      </c>
+      <c r="D37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" t="s">
+        <v>392</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="B37" t="s">
-        <v>394</v>
-      </c>
-      <c r="C37" t="s">
-        <v>395</v>
-      </c>
-      <c r="D37" t="s">
-        <v>207</v>
-      </c>
-      <c r="E37" t="s">
-        <v>396</v>
-      </c>
-      <c r="F37" t="s">
-        <v>397</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C38" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D38" t="s">
         <v>207</v>
       </c>
       <c r="E38" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F38" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>399</v>
+      </c>
+      <c r="B39" t="s">
+        <v>400</v>
+      </c>
+      <c r="C39" t="s">
+        <v>401</v>
+      </c>
+      <c r="D39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" t="s">
+        <v>402</v>
+      </c>
+      <c r="F39" t="s">
         <v>403</v>
       </c>
-      <c r="B39" t="s">
+      <c r="H39" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="C39" t="s">
-        <v>231</v>
-      </c>
-      <c r="D39" t="s">
-        <v>207</v>
-      </c>
-      <c r="E39" t="s">
-        <v>405</v>
-      </c>
-      <c r="F39" t="s">
-        <v>406</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>399</v>
+      </c>
+      <c r="B40" t="s">
+        <v>405</v>
+      </c>
+      <c r="C40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D40" t="s">
+        <v>207</v>
+      </c>
+      <c r="E40" t="s">
+        <v>406</v>
+      </c>
+      <c r="F40" t="s">
+        <v>407</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="B40" t="s">
-        <v>409</v>
-      </c>
-      <c r="C40" t="s">
-        <v>410</v>
-      </c>
-      <c r="D40" t="s">
-        <v>207</v>
-      </c>
-      <c r="E40" t="s">
-        <v>411</v>
-      </c>
-      <c r="F40" t="s">
-        <v>412</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C41" t="s">
-        <v>416</v>
+        <v>231</v>
       </c>
       <c r="D41" t="s">
         <v>207</v>
       </c>
       <c r="E41" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F41" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>415</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>416</v>
       </c>
       <c r="D42" t="s">
         <v>207</v>
       </c>
       <c r="E42" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F42" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>420</v>
+      </c>
+      <c r="B43" t="s">
+        <v>421</v>
+      </c>
+      <c r="C43" t="s">
+        <v>422</v>
+      </c>
+      <c r="D43" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" t="s">
+        <v>423</v>
+      </c>
+      <c r="F43" t="s">
         <v>424</v>
       </c>
-      <c r="B43" t="s">
-        <v>258</v>
-      </c>
-      <c r="C43" t="s">
-        <v>195</v>
-      </c>
-      <c r="D43" t="s">
-        <v>207</v>
-      </c>
-      <c r="E43" t="s">
-        <v>421</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="H43" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>426</v>
+      </c>
+      <c r="B44" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" t="s">
+        <v>195</v>
+      </c>
+      <c r="D44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" t="s">
         <v>427</v>
       </c>
-      <c r="B44" t="s">
+      <c r="F44" t="s">
         <v>428</v>
       </c>
-      <c r="C44" t="s">
-        <v>225</v>
-      </c>
-      <c r="D44" t="s">
-        <v>207</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="H44" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="F44" t="s">
-        <v>430</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>430</v>
+      </c>
+      <c r="B45" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" t="s">
+        <v>207</v>
+      </c>
+      <c r="E45" t="s">
+        <v>427</v>
+      </c>
+      <c r="F45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="B45" t="s">
-        <v>433</v>
-      </c>
-      <c r="C45" t="s">
-        <v>434</v>
-      </c>
-      <c r="D45" t="s">
-        <v>435</v>
-      </c>
-      <c r="E45" t="s">
-        <v>436</v>
-      </c>
-      <c r="F45" t="s">
-        <v>437</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>434</v>
       </c>
       <c r="C46" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D46" t="s">
         <v>207</v>
       </c>
       <c r="E46" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F46" t="s">
-        <v>277</v>
+        <v>436</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>438</v>
+      </c>
+      <c r="B47" t="s">
+        <v>439</v>
+      </c>
+      <c r="C47" t="s">
+        <v>440</v>
+      </c>
+      <c r="D47" t="s">
+        <v>441</v>
+      </c>
+      <c r="E47" t="s">
         <v>442</v>
       </c>
-      <c r="B47" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" t="s">
-        <v>195</v>
-      </c>
-      <c r="D47" t="s">
-        <v>207</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>443</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s">
-        <v>447</v>
+        <v>275</v>
       </c>
       <c r="C48" t="s">
         <v>231</v>
@@ -5060,82 +5081,82 @@
         <v>207</v>
       </c>
       <c r="E48" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F48" t="s">
-        <v>449</v>
+        <v>277</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>448</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" t="s">
+        <v>207</v>
+      </c>
+      <c r="E49" t="s">
+        <v>449</v>
+      </c>
+      <c r="F49" t="s">
+        <v>450</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="B49" t="s">
-        <v>452</v>
-      </c>
-      <c r="C49" t="s">
-        <v>453</v>
-      </c>
-      <c r="D49" t="s">
-        <v>207</v>
-      </c>
-      <c r="E49" t="s">
-        <v>454</v>
-      </c>
-      <c r="F49" t="s">
-        <v>189</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>199</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s">
+        <v>453</v>
+      </c>
+      <c r="C50" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" t="s">
+        <v>207</v>
+      </c>
+      <c r="E50" t="s">
+        <v>454</v>
+      </c>
+      <c r="F50" t="s">
+        <v>455</v>
+      </c>
+      <c r="H50" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="C50" t="s">
-        <v>457</v>
-      </c>
-      <c r="D50" t="s">
-        <v>207</v>
-      </c>
-      <c r="E50" t="s">
-        <v>458</v>
-      </c>
-      <c r="F50" t="s">
-        <v>459</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>199</v>
+        <v>457</v>
       </c>
       <c r="B51" t="s">
+        <v>458</v>
+      </c>
+      <c r="C51" t="s">
+        <v>459</v>
+      </c>
+      <c r="D51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E51" t="s">
+        <v>460</v>
+      </c>
+      <c r="F51" t="s">
+        <v>189</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C51" t="s">
-        <v>293</v>
-      </c>
-      <c r="D51" t="s">
-        <v>207</v>
-      </c>
-      <c r="E51" t="s">
-        <v>462</v>
-      </c>
-      <c r="F51" t="s">
-        <v>463</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -5143,22 +5164,22 @@
         <v>199</v>
       </c>
       <c r="B52" t="s">
+        <v>462</v>
+      </c>
+      <c r="C52" t="s">
+        <v>463</v>
+      </c>
+      <c r="D52" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" t="s">
+        <v>464</v>
+      </c>
+      <c r="F52" t="s">
         <v>465</v>
       </c>
-      <c r="C52" t="s">
+      <c r="H52" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="D52" t="s">
-        <v>207</v>
-      </c>
-      <c r="E52" t="s">
-        <v>467</v>
-      </c>
-      <c r="F52" t="s">
-        <v>468</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -5166,22 +5187,22 @@
         <v>199</v>
       </c>
       <c r="B53" t="s">
+        <v>467</v>
+      </c>
+      <c r="C53" t="s">
+        <v>295</v>
+      </c>
+      <c r="D53" t="s">
+        <v>207</v>
+      </c>
+      <c r="E53" t="s">
+        <v>468</v>
+      </c>
+      <c r="F53" t="s">
+        <v>469</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="C53" t="s">
-        <v>471</v>
-      </c>
-      <c r="D53" t="s">
-        <v>207</v>
-      </c>
-      <c r="E53" t="s">
-        <v>189</v>
-      </c>
-      <c r="F53" t="s">
-        <v>189</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -5189,22 +5210,22 @@
         <v>199</v>
       </c>
       <c r="B54" t="s">
+        <v>471</v>
+      </c>
+      <c r="C54" t="s">
+        <v>472</v>
+      </c>
+      <c r="D54" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" t="s">
         <v>473</v>
       </c>
-      <c r="C54" t="s">
+      <c r="F54" t="s">
         <v>474</v>
       </c>
-      <c r="D54" t="s">
-        <v>207</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="H54" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="F54" t="s">
-        <v>476</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -5212,1456 +5233,1456 @@
         <v>199</v>
       </c>
       <c r="B55" t="s">
+        <v>476</v>
+      </c>
+      <c r="C55" t="s">
+        <v>477</v>
+      </c>
+      <c r="D55" t="s">
+        <v>207</v>
+      </c>
+      <c r="E55" t="s">
+        <v>189</v>
+      </c>
+      <c r="F55" t="s">
+        <v>189</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="C55" t="s">
-        <v>479</v>
-      </c>
-      <c r="D55" t="s">
-        <v>270</v>
-      </c>
-      <c r="E55" t="s">
-        <v>480</v>
-      </c>
-      <c r="F55" t="s">
-        <v>481</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" t="s">
+        <v>479</v>
+      </c>
+      <c r="C56" t="s">
+        <v>480</v>
+      </c>
+      <c r="D56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56" t="s">
+        <v>481</v>
+      </c>
+      <c r="F56" t="s">
+        <v>482</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="B56" t="s">
-        <v>484</v>
-      </c>
-      <c r="C56" t="s">
-        <v>485</v>
-      </c>
-      <c r="D56" t="s">
-        <v>207</v>
-      </c>
-      <c r="E56" t="s">
-        <v>486</v>
-      </c>
-      <c r="F56" t="s">
-        <v>459</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" t="s">
+        <v>484</v>
+      </c>
+      <c r="C57" t="s">
+        <v>485</v>
+      </c>
+      <c r="D57" t="s">
+        <v>270</v>
+      </c>
+      <c r="E57" t="s">
+        <v>486</v>
+      </c>
+      <c r="F57" t="s">
+        <v>487</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="B57" t="s">
-        <v>489</v>
-      </c>
-      <c r="C57" t="s">
-        <v>195</v>
-      </c>
-      <c r="D57" t="s">
-        <v>207</v>
-      </c>
-      <c r="E57" t="s">
-        <v>324</v>
-      </c>
-      <c r="F57" t="s">
-        <v>189</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" t="s">
+        <v>489</v>
+      </c>
+      <c r="C58" t="s">
+        <v>490</v>
+      </c>
+      <c r="D58" t="s">
+        <v>207</v>
+      </c>
+      <c r="E58" t="s">
+        <v>481</v>
+      </c>
+      <c r="F58" t="s">
+        <v>482</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="B58" t="s">
-        <v>492</v>
-      </c>
-      <c r="C58" t="s">
-        <v>493</v>
-      </c>
-      <c r="D58" t="s">
-        <v>435</v>
-      </c>
-      <c r="E58" t="s">
-        <v>494</v>
-      </c>
-      <c r="F58" t="s">
-        <v>495</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B59" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C59" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="D59" t="s">
         <v>207</v>
       </c>
       <c r="E59" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F59" t="s">
-        <v>251</v>
+        <v>465</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C60" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D60" t="s">
         <v>207</v>
       </c>
       <c r="E60" t="s">
-        <v>504</v>
+        <v>326</v>
       </c>
       <c r="F60" t="s">
-        <v>505</v>
+        <v>189</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="B61" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C61" t="s">
-        <v>231</v>
+        <v>502</v>
       </c>
       <c r="D61" t="s">
-        <v>270</v>
+        <v>441</v>
       </c>
       <c r="E61" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F61" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B62" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="C62" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D62" t="s">
         <v>207</v>
       </c>
       <c r="E62" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F62" t="s">
-        <v>516</v>
+        <v>251</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C63" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E63" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="F63" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C64" t="s">
-        <v>357</v>
+        <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="E64" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F64" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B65" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C65" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="D65" t="s">
         <v>207</v>
       </c>
       <c r="E65" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F65" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B66" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="C66" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D66" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E66" t="s">
-        <v>244</v>
+        <v>529</v>
       </c>
       <c r="F66" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B67" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C67" t="s">
-        <v>540</v>
+        <v>363</v>
       </c>
       <c r="D67" t="s">
-        <v>435</v>
+        <v>207</v>
       </c>
       <c r="E67" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="F67" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B68" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C68" t="s">
-        <v>231</v>
+        <v>539</v>
       </c>
       <c r="D68" t="s">
         <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="F68" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B69" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="C69" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D69" t="s">
         <v>207</v>
       </c>
       <c r="E69" t="s">
-        <v>551</v>
+        <v>244</v>
       </c>
       <c r="F69" t="s">
-        <v>227</v>
+        <v>545</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B70" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C70" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D70" t="s">
-        <v>232</v>
+        <v>441</v>
       </c>
       <c r="E70" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="F70" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B71" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="C71" t="s">
-        <v>561</v>
+        <v>231</v>
       </c>
       <c r="D71" t="s">
         <v>207</v>
       </c>
       <c r="E71" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="F71" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="B72" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C72" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D72" t="s">
         <v>207</v>
       </c>
       <c r="E72" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="F72" t="s">
-        <v>568</v>
+        <v>227</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="B73" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C73" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="D73" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E73" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="F73" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B74" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C74" t="s">
-        <v>249</v>
+        <v>570</v>
       </c>
       <c r="D74" t="s">
         <v>207</v>
       </c>
       <c r="E74" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="F74" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="C75" t="s">
-        <v>583</v>
+        <v>231</v>
       </c>
       <c r="D75" t="s">
         <v>207</v>
       </c>
       <c r="E75" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="F75" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B76" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>581</v>
       </c>
       <c r="D76" t="s">
         <v>207</v>
       </c>
       <c r="E76" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="F76" t="s">
-        <v>189</v>
+        <v>583</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B77" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C77" t="s">
-        <v>379</v>
+        <v>249</v>
       </c>
       <c r="D77" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="E77" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="F77" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="B78" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C78" t="s">
-        <v>225</v>
+        <v>592</v>
       </c>
       <c r="D78" t="s">
         <v>207</v>
       </c>
       <c r="E78" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="F78" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B79" t="s">
-        <v>399</v>
+        <v>335</v>
       </c>
       <c r="C79" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D79" t="s">
         <v>207</v>
       </c>
       <c r="E79" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="F79" t="s">
-        <v>401</v>
+        <v>189</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B80" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>385</v>
       </c>
       <c r="D80" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="E80" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="F80" t="s">
-        <v>227</v>
+        <v>601</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>603</v>
+      </c>
+      <c r="B81" t="s">
+        <v>604</v>
+      </c>
+      <c r="C81" t="s">
+        <v>225</v>
+      </c>
+      <c r="D81" t="s">
+        <v>207</v>
+      </c>
+      <c r="E81" t="s">
+        <v>605</v>
+      </c>
+      <c r="F81" t="s">
+        <v>606</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B81" t="s">
-        <v>608</v>
-      </c>
-      <c r="C81" t="s">
-        <v>255</v>
-      </c>
-      <c r="D81" t="s">
-        <v>207</v>
-      </c>
-      <c r="E81" t="s">
-        <v>609</v>
-      </c>
-      <c r="F81" t="s">
-        <v>610</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s">
-        <v>613</v>
+        <v>405</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D82" t="s">
         <v>207</v>
       </c>
       <c r="E82" t="s">
-        <v>614</v>
+        <v>347</v>
       </c>
       <c r="F82" t="s">
-        <v>615</v>
+        <v>407</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B83" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="D83" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E83" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="F83" t="s">
-        <v>620</v>
+        <v>227</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B84" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D84" t="s">
         <v>207</v>
       </c>
       <c r="E84" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
       <c r="F84" t="s">
-        <v>526</v>
+        <v>617</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B85" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="C85" t="s">
-        <v>627</v>
+        <v>195</v>
       </c>
       <c r="D85" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E85" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="F85" t="s">
-        <v>320</v>
+        <v>622</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B86" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C86" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="D86" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E86" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="F86" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C87" t="s">
-        <v>572</v>
+        <v>249</v>
       </c>
       <c r="D87" t="s">
         <v>207</v>
       </c>
       <c r="E87" t="s">
-        <v>454</v>
+        <v>524</v>
       </c>
       <c r="F87" t="s">
-        <v>574</v>
+        <v>535</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="B88" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C88" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D88" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="E88" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="F88" t="s">
-        <v>642</v>
+        <v>322</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="B89" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="C89" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="D89" t="s">
         <v>207</v>
       </c>
       <c r="E89" t="s">
-        <v>458</v>
+        <v>639</v>
       </c>
       <c r="F89" t="s">
-        <v>526</v>
+        <v>640</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B90" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C90" t="s">
-        <v>231</v>
+        <v>581</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="E90" t="s">
-        <v>648</v>
+        <v>460</v>
       </c>
       <c r="F90" t="s">
-        <v>649</v>
+        <v>583</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B91" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C91" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="D91" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="E91" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="F91" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="B92" t="s">
-        <v>658</v>
+        <v>630</v>
       </c>
       <c r="C92" t="s">
-        <v>659</v>
+        <v>249</v>
       </c>
       <c r="D92" t="s">
-        <v>435</v>
+        <v>207</v>
       </c>
       <c r="E92" t="s">
-        <v>660</v>
+        <v>464</v>
       </c>
       <c r="F92" t="s">
-        <v>661</v>
+        <v>535</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="B93" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="C93" t="s">
         <v>231</v>
       </c>
       <c r="D93" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="E93" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="F93" t="s">
-        <v>260</v>
+        <v>656</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="B94" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C94" t="s">
-        <v>195</v>
+        <v>660</v>
       </c>
       <c r="D94" t="s">
         <v>207</v>
       </c>
       <c r="E94" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="F94" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="B95" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="C95" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="D95" t="s">
-        <v>207</v>
+        <v>441</v>
       </c>
       <c r="E95" t="s">
-        <v>288</v>
+        <v>667</v>
       </c>
       <c r="F95" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="B96" t="s">
-        <v>248</v>
+        <v>671</v>
       </c>
       <c r="C96" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D96" t="s">
-        <v>435</v>
+        <v>207</v>
       </c>
       <c r="E96" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="F96" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B97" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C97" t="s">
-        <v>682</v>
+        <v>195</v>
       </c>
       <c r="D97" t="s">
         <v>207</v>
       </c>
       <c r="E97" t="s">
-        <v>475</v>
+        <v>676</v>
       </c>
       <c r="F97" t="s">
-        <v>320</v>
+        <v>677</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B98" t="s">
-        <v>243</v>
+        <v>680</v>
       </c>
       <c r="C98" t="s">
-        <v>231</v>
+        <v>681</v>
       </c>
       <c r="D98" t="s">
         <v>207</v>
       </c>
       <c r="E98" t="s">
-        <v>685</v>
+        <v>290</v>
       </c>
       <c r="F98" t="s">
-        <v>245</v>
+        <v>682</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B99" t="s">
-        <v>688</v>
+        <v>248</v>
       </c>
       <c r="C99" t="s">
-        <v>689</v>
+        <v>249</v>
       </c>
       <c r="D99" t="s">
-        <v>207</v>
+        <v>441</v>
       </c>
       <c r="E99" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F99" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B100" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="C100" t="s">
-        <v>340</v>
+        <v>689</v>
       </c>
       <c r="D100" t="s">
         <v>207</v>
       </c>
       <c r="E100" t="s">
-        <v>324</v>
+        <v>481</v>
       </c>
       <c r="F100" t="s">
-        <v>694</v>
+        <v>322</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B101" t="s">
-        <v>697</v>
+        <v>243</v>
       </c>
       <c r="C101" t="s">
-        <v>698</v>
+        <v>231</v>
       </c>
       <c r="D101" t="s">
         <v>207</v>
       </c>
       <c r="E101" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="F101" t="s">
-        <v>536</v>
+        <v>245</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B102" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C102" t="s">
-        <v>255</v>
+        <v>696</v>
       </c>
       <c r="D102" t="s">
         <v>207</v>
       </c>
       <c r="E102" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="F102" t="s">
-        <v>704</v>
+        <v>189</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B103" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C103" t="s">
-        <v>195</v>
+        <v>346</v>
       </c>
       <c r="D103" t="s">
         <v>207</v>
       </c>
       <c r="E103" t="s">
-        <v>708</v>
+        <v>326</v>
       </c>
       <c r="F103" t="s">
-        <v>468</v>
+        <v>701</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="B104" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="C104" t="s">
-        <v>231</v>
+        <v>705</v>
       </c>
       <c r="D104" t="s">
         <v>207</v>
       </c>
       <c r="E104" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="F104" t="s">
-        <v>713</v>
+        <v>545</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="B105" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C105" t="s">
-        <v>717</v>
+        <v>255</v>
       </c>
       <c r="D105" t="s">
         <v>207</v>
       </c>
       <c r="E105" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="F105" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="B106" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C106" t="s">
-        <v>717</v>
+        <v>195</v>
       </c>
       <c r="D106" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="E106" t="s">
-        <v>619</v>
+        <v>715</v>
       </c>
       <c r="F106" t="s">
-        <v>723</v>
+        <v>474</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B107" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="C107" t="s">
-        <v>727</v>
+        <v>231</v>
       </c>
       <c r="D107" t="s">
         <v>207</v>
       </c>
       <c r="E107" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="F107" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="B108" t="s">
-        <v>652</v>
+        <v>723</v>
       </c>
       <c r="C108" t="s">
-        <v>653</v>
+        <v>724</v>
       </c>
       <c r="D108" t="s">
         <v>207</v>
       </c>
       <c r="E108" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="F108" t="s">
-        <v>655</v>
+        <v>726</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B109" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C109" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="D109" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="E109" t="s">
-        <v>189</v>
+        <v>626</v>
       </c>
       <c r="F109" t="s">
-        <v>189</v>
+        <v>730</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="B110" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C110" t="s">
-        <v>231</v>
+        <v>734</v>
       </c>
       <c r="D110" t="s">
         <v>207</v>
       </c>
       <c r="E110" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="F110" t="s">
-        <v>320</v>
+        <v>736</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B111" t="s">
-        <v>743</v>
+        <v>659</v>
       </c>
       <c r="C111" t="s">
-        <v>744</v>
+        <v>660</v>
       </c>
       <c r="D111" t="s">
         <v>207</v>
       </c>
       <c r="E111" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="F111" t="s">
-        <v>746</v>
+        <v>662</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B112" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="C112" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="D112" t="s">
         <v>207</v>
       </c>
       <c r="E112" t="s">
-        <v>751</v>
+        <v>189</v>
       </c>
       <c r="F112" t="s">
         <v>189</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="B113" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="C113" t="s">
-        <v>755</v>
+        <v>231</v>
       </c>
       <c r="D113" t="s">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="E113" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="F113" t="s">
-        <v>189</v>
+        <v>322</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>749</v>
+      </c>
+      <c r="B114" t="s">
+        <v>750</v>
+      </c>
+      <c r="C114" t="s">
+        <v>751</v>
+      </c>
+      <c r="D114" t="s">
+        <v>207</v>
+      </c>
+      <c r="E114" t="s">
+        <v>752</v>
+      </c>
+      <c r="F114" t="s">
         <v>753</v>
       </c>
-      <c r="B114" t="s">
+      <c r="H114" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="C114" t="s">
-        <v>758</v>
-      </c>
-      <c r="D114" t="s">
-        <v>270</v>
-      </c>
-      <c r="E114" t="s">
-        <v>759</v>
-      </c>
-      <c r="F114" t="s">
-        <v>760</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="B115" t="s">
-        <v>275</v>
+        <v>756</v>
       </c>
       <c r="C115" t="s">
-        <v>231</v>
+        <v>757</v>
       </c>
       <c r="D115" t="s">
         <v>207</v>
       </c>
       <c r="E115" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="F115" t="s">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B116" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C116" t="s">
-        <v>231</v>
+        <v>762</v>
       </c>
       <c r="D116" t="s">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="E116" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F116" t="s">
         <v>189</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="B117" t="s">
+        <v>761</v>
+      </c>
+      <c r="C117" t="s">
+        <v>765</v>
+      </c>
+      <c r="D117" t="s">
+        <v>270</v>
+      </c>
+      <c r="E117" t="s">
         <v>766</v>
       </c>
-      <c r="C117" t="s">
-        <v>770</v>
-      </c>
-      <c r="D117" t="s">
-        <v>207</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>767</v>
       </c>
-      <c r="F117" t="s">
-        <v>189</v>
-      </c>
       <c r="H117" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B118" t="s">
-        <v>773</v>
+        <v>275</v>
       </c>
       <c r="C118" t="s">
         <v>231</v>
@@ -6670,102 +6691,102 @@
         <v>207</v>
       </c>
       <c r="E118" t="s">
-        <v>685</v>
+        <v>770</v>
       </c>
       <c r="F118" t="s">
-        <v>774</v>
+        <v>277</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B119" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C119" t="s">
-        <v>778</v>
+        <v>231</v>
       </c>
       <c r="D119" t="s">
         <v>207</v>
       </c>
       <c r="E119" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="F119" t="s">
-        <v>661</v>
+        <v>189</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="B120" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="C120" t="s">
-        <v>225</v>
+        <v>777</v>
       </c>
       <c r="D120" t="s">
         <v>207</v>
       </c>
       <c r="E120" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="F120" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>779</v>
+      </c>
+      <c r="B121" t="s">
+        <v>780</v>
+      </c>
+      <c r="C121" t="s">
+        <v>231</v>
+      </c>
+      <c r="D121" t="s">
+        <v>207</v>
+      </c>
+      <c r="E121" t="s">
+        <v>692</v>
+      </c>
+      <c r="F121" t="s">
         <v>781</v>
       </c>
-      <c r="B121" t="s">
+      <c r="H121" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="C121" t="s">
-        <v>572</v>
-      </c>
-      <c r="D121" t="s">
-        <v>207</v>
-      </c>
-      <c r="E121" t="s">
-        <v>783</v>
-      </c>
-      <c r="F121" t="s">
-        <v>227</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B122" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C122" t="s">
+        <v>785</v>
+      </c>
+      <c r="D122" t="s">
+        <v>207</v>
+      </c>
+      <c r="E122" t="s">
         <v>786</v>
       </c>
-      <c r="D122" t="s">
-        <v>207</v>
-      </c>
-      <c r="E122" t="s">
-        <v>783</v>
-      </c>
       <c r="F122" t="s">
-        <v>227</v>
+        <v>668</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>787</v>
@@ -6773,232 +6794,301 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B123" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="C123" t="s">
-        <v>788</v>
+        <v>225</v>
       </c>
       <c r="D123" t="s">
         <v>207</v>
       </c>
       <c r="E123" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="F123" t="s">
         <v>227</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>788</v>
+      </c>
+      <c r="B124" t="s">
+        <v>789</v>
+      </c>
+      <c r="C124" t="s">
+        <v>581</v>
+      </c>
+      <c r="D124" t="s">
+        <v>207</v>
+      </c>
+      <c r="E124" t="s">
         <v>790</v>
       </c>
-      <c r="B124" t="s">
-        <v>791</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="F124" t="s">
+        <v>227</v>
+      </c>
+      <c r="H124" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="D124" t="s">
-        <v>207</v>
-      </c>
-      <c r="E124" t="s">
-        <v>189</v>
-      </c>
-      <c r="F124" t="s">
-        <v>189</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>788</v>
+      </c>
+      <c r="B125" t="s">
+        <v>789</v>
+      </c>
+      <c r="C125" t="s">
+        <v>793</v>
+      </c>
+      <c r="D125" t="s">
+        <v>207</v>
+      </c>
+      <c r="E125" t="s">
+        <v>790</v>
+      </c>
+      <c r="F125" t="s">
+        <v>227</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="B125" t="s">
-        <v>613</v>
-      </c>
-      <c r="C125" t="s">
-        <v>195</v>
-      </c>
-      <c r="D125" t="s">
-        <v>239</v>
-      </c>
-      <c r="E125" t="s">
-        <v>795</v>
-      </c>
-      <c r="F125" t="s">
-        <v>796</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
       <c r="B126" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="C126" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="D126" t="s">
         <v>207</v>
       </c>
       <c r="E126" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="F126" t="s">
-        <v>802</v>
+        <v>227</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="B127" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="C127" t="s">
-        <v>231</v>
+        <v>799</v>
       </c>
       <c r="D127" t="s">
         <v>207</v>
       </c>
       <c r="E127" t="s">
-        <v>806</v>
+        <v>189</v>
       </c>
       <c r="F127" t="s">
-        <v>807</v>
+        <v>189</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B128" t="s">
-        <v>805</v>
+        <v>620</v>
       </c>
       <c r="C128" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="D128" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="E128" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="F128" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="B129" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="C129" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="D129" t="s">
         <v>207</v>
       </c>
       <c r="E129" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="F129" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="B130" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="C130" t="s">
-        <v>820</v>
+        <v>231</v>
       </c>
       <c r="D130" t="s">
         <v>207</v>
       </c>
       <c r="E130" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="F130" t="s">
-        <v>189</v>
+        <v>814</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="B131" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="C131" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="D131" t="s">
         <v>207</v>
       </c>
       <c r="E131" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="F131" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>819</v>
+      </c>
+      <c r="B132" t="s">
+        <v>820</v>
+      </c>
+      <c r="C132" t="s">
+        <v>821</v>
+      </c>
+      <c r="D132" t="s">
+        <v>207</v>
+      </c>
+      <c r="E132" t="s">
+        <v>822</v>
+      </c>
+      <c r="F132" t="s">
+        <v>823</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>825</v>
+      </c>
+      <c r="B133" t="s">
+        <v>826</v>
+      </c>
+      <c r="C133" t="s">
+        <v>827</v>
+      </c>
+      <c r="D133" t="s">
+        <v>207</v>
+      </c>
+      <c r="E133" t="s">
         <v>828</v>
       </c>
-      <c r="B132" t="s">
+      <c r="F133" t="s">
+        <v>189</v>
+      </c>
+      <c r="H133" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="C132" t="s">
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>830</v>
       </c>
-      <c r="D132" t="s">
+      <c r="B134" t="s">
+        <v>831</v>
+      </c>
+      <c r="C134" t="s">
+        <v>195</v>
+      </c>
+      <c r="D134" t="s">
+        <v>207</v>
+      </c>
+      <c r="E134" t="s">
+        <v>832</v>
+      </c>
+      <c r="F134" t="s">
+        <v>833</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>835</v>
+      </c>
+      <c r="B135" t="s">
+        <v>836</v>
+      </c>
+      <c r="C135" t="s">
+        <v>837</v>
+      </c>
+      <c r="D135" t="s">
         <v>270</v>
       </c>
-      <c r="E132" t="s">
-        <v>831</v>
-      </c>
-      <c r="F132" t="s">
-        <v>832</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>833</v>
+      <c r="E135" t="s">
+        <v>838</v>
+      </c>
+      <c r="F135" t="s">
+        <v>839</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -7135,6 +7225,9 @@
     <hyperlink ref="H130" r:id="rId129"/>
     <hyperlink ref="H131" r:id="rId130"/>
     <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7184,13 +7277,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="B2" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C2" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="D2" t="s">
         <v>189</v>
@@ -7199,21 +7292,21 @@
         <v>189</v>
       </c>
       <c r="F2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="B3" t="s">
         <v>186</v>
       </c>
       <c r="C3" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="D3" t="s">
         <v>189</v>
@@ -7222,24 +7315,24 @@
         <v>189</v>
       </c>
       <c r="F3" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="G3" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="B4" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="C4" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="D4" t="s">
         <v>189</v>
@@ -7248,21 +7341,21 @@
         <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="B5" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="C5" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="D5" t="s">
         <v>189</v>
@@ -7271,21 +7364,21 @@
         <v>189</v>
       </c>
       <c r="F5" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="B6" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="C6" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="D6" t="s">
         <v>189</v>
@@ -7294,21 +7387,21 @@
         <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B7" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="C7" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="D7" t="s">
         <v>189</v>
@@ -7317,21 +7410,21 @@
         <v>189</v>
       </c>
       <c r="F7" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="B8" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="C8" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="D8" t="s">
         <v>189</v>
@@ -7340,21 +7433,21 @@
         <v>189</v>
       </c>
       <c r="F8" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="B9" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="C9" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="D9" t="s">
         <v>189</v>
@@ -7363,21 +7456,21 @@
         <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="B10" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="C10" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="D10" t="s">
         <v>189</v>
@@ -7386,21 +7479,21 @@
         <v>189</v>
       </c>
       <c r="F10" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="B11" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="C11" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="D11" t="s">
         <v>189</v>
@@ -7409,21 +7502,21 @@
         <v>189</v>
       </c>
       <c r="F11" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="B12" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D12" t="s">
         <v>189</v>
@@ -7432,21 +7525,21 @@
         <v>189</v>
       </c>
       <c r="F12" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="B13" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="C13" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D13" t="s">
         <v>189</v>
@@ -7455,10 +7548,10 @@
         <v>189</v>
       </c>
       <c r="F13" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
     </row>
   </sheetData>
